--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -2199,13 +2199,13 @@
     <t>Стол рабочий с подкатной тумбой (ZETA Лофт)</t>
   </si>
   <si>
-    <t>в бюджете 20 столов на 17 новых сотрудников 2026 года – запас 3</t>
+    <t>в бюджете 20 столов на 18 новых сотрудников 2026 года – запас 2</t>
   </si>
   <si>
     <t>Кресло рабочее (МИ-6 Z)</t>
   </si>
   <si>
-    <t>в бюджете 26 кресел на 17 сотрудников и 7 аутсорсеров – запас 2</t>
+    <t>в бюджете 26 кресел на 18 сотрудников и 7 аутсорсеров – запас 1</t>
   </si>
   <si>
     <t>Сетевые фильтры на рабочие места</t>
@@ -3025,19 +3025,19 @@
       </c>
       <c r="B4" s="37">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=2))</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="37">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=3))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="37">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=3))</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="37">
         <f>D4+COUNT('Февраль 2027'!D4:D10)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="37"/>
     </row>
@@ -3060,23 +3060,23 @@
       </c>
       <c r="B6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+B20</f>
-        <v>63001690</v>
+        <v>64149240</v>
       </c>
       <c r="C6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3)))+C7+C20</f>
-        <v>36424100</v>
+        <v>37571650</v>
       </c>
       <c r="D6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3)))+D7+D20</f>
-        <v>27034580</v>
+        <v>28182130</v>
       </c>
       <c r="E6" s="38">
         <f>D6+'Февраль 2027'!F11</f>
-        <v>33837850</v>
+        <v>34985400</v>
       </c>
       <c r="F6" s="38">
         <f>SUM(B6:E6)</f>
-        <v>160298220</v>
+        <v>164888420</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B9" s="38">
         <f>Штат!$N$37</f>
-        <v>611142.85714285716</v>
+        <v>645095.23809523811</v>
       </c>
       <c r="C9" s="38">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="F9" s="38">
         <f>SUM(B9:E9)</f>
-        <v>816142.85714285716</v>
+        <v>850095.23809523811</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3192,11 +3192,11 @@
       </c>
       <c r="E11" s="38">
         <f>'Февраль 2027'!F19</f>
-        <v>412690</v>
+        <v>505594</v>
       </c>
       <c r="F11" s="38">
         <f>SUM(B11:E11)</f>
-        <v>14444732.9</v>
+        <v>14537636.9</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3280,23 +3280,23 @@
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)-B7</f>
-        <v>98068022.855529949</v>
+        <v>99249525.236482337</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)-C7</f>
-        <v>53542054.350000001</v>
+        <v>54689604.350000001</v>
       </c>
       <c r="D15" s="40">
         <f>SUM(D6:D14)-D7</f>
-        <v>42516269.100000001</v>
+        <v>43663819.100000001</v>
       </c>
       <c r="E15" s="40">
         <f>SUM(E6:E14)-E7</f>
-        <v>50582291.600000001</v>
+        <v>51822745.600000001</v>
       </c>
       <c r="F15" s="40">
         <f>SUM(B15:E15)</f>
-        <v>244708637.90552995</v>
+        <v>249425694.28648233</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3305,23 +3305,23 @@
       </c>
       <c r="B16" s="38">
         <f>(B15-B20)*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>6411802.2855529953</v>
+        <v>6529952.5236482341</v>
       </c>
       <c r="C16" s="38">
         <f>(C15-C20)*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>5354205.4350000005</v>
+        <v>5468960.4350000005</v>
       </c>
       <c r="D16" s="38">
         <f>(D15-D20)*Резерв+SUMIFS('Оснащение и офис'!$L$5:$L$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>4251626.91</v>
+        <v>4366381.91</v>
       </c>
       <c r="E16" s="38">
         <f>(E15-E20)*Резерв</f>
-        <v>5058229.16</v>
+        <v>5182274.5600000005</v>
       </c>
       <c r="F16" s="38">
         <f>SUM(B16:E16)</f>
-        <v>21075863.790552996</v>
+        <v>21547569.428648233</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3342,11 +3342,11 @@
       </c>
       <c r="E17" s="38">
         <f>(E11+E12+E13+E14)*(1+Резерв)*НДС</f>
-        <v>1250116.2256</v>
+        <v>1266467.3296000001</v>
       </c>
       <c r="F17" s="38">
         <f>SUM(B17:E17)</f>
-        <v>7547929.65491613</v>
+        <v>7564280.7589161294</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3355,23 +3355,23 @@
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
-        <v>108141493.81519908</v>
+        <v>109441146.4342467</v>
       </c>
       <c r="C18" s="42">
         <f>C15+C16+C17</f>
-        <v>60363545.754600003</v>
+        <v>61625850.754600003</v>
       </c>
       <c r="D18" s="42">
         <f>D15+D16+D17</f>
-        <v>47936754.795600004</v>
+        <v>49199059.795600004</v>
       </c>
       <c r="E18" s="42">
         <f>E15+E16+E17</f>
-        <v>56890636.985600002</v>
+        <v>58271487.489600003</v>
       </c>
       <c r="F18" s="42">
         <f>SUM(B18:E18)</f>
-        <v>273332431.35099906</v>
+        <v>278537544.47404671</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3426,23 +3426,23 @@
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
-        <v>146387467.14853242</v>
+        <v>147687119.76758003</v>
       </c>
       <c r="C21" s="44">
         <f>C18+C19</f>
-        <v>92194719.087933332</v>
+        <v>93457024.087933332</v>
       </c>
       <c r="D21" s="44">
         <f>D18+D19</f>
-        <v>65093928.12893334</v>
+        <v>66356233.12893334</v>
       </c>
       <c r="E21" s="44">
         <f>E18+E19</f>
-        <v>85968743.652266666</v>
+        <v>87349594.156266674</v>
       </c>
       <c r="F21" s="44">
         <f>F18+F19</f>
-        <v>389644858.01766574</v>
+        <v>394849971.14071339</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3451,19 +3451,19 @@
       </c>
       <c r="B23" s="44">
         <f>B21</f>
-        <v>146387467.14853242</v>
+        <v>147687119.76758003</v>
       </c>
       <c r="C23" s="44">
         <f>B23+C21</f>
-        <v>238582186.23646575</v>
+        <v>241144143.85551336</v>
       </c>
       <c r="D23" s="44">
         <f>C23+D21</f>
-        <v>303676114.36539912</v>
+        <v>307500376.9844467</v>
       </c>
       <c r="E23" s="44">
         <f>D23+E21</f>
-        <v>389644858.0176658</v>
+        <v>394849971.14071339</v>
       </c>
       <c r="F23" s="44"/>
     </row>
@@ -3485,23 +3485,23 @@
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
-        <v>103612532.85146758</v>
+        <v>102312880.23241997</v>
       </c>
       <c r="C25" s="44">
         <f>$F$24-C23</f>
-        <v>11417813.763534248</v>
+        <v>8855856.1444866359</v>
       </c>
       <c r="D25" s="44">
         <f>$F$24-D23</f>
-        <v>-53676114.365399122</v>
+        <v>-57500376.984446704</v>
       </c>
       <c r="E25" s="44">
         <f>$F$24-E23</f>
-        <v>-139644858.0176658</v>
+        <v>-144849971.14071339</v>
       </c>
       <c r="F25" s="44">
         <f>F24-F21</f>
-        <v>-139644858.01766574</v>
+        <v>-144849971.14071339</v>
       </c>
     </row>
   </sheetData>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C15" s="111"/>
       <c r="D15" s="112">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" s="112">
         <f>'Оснащение и офис'!E8</f>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="F15" s="112">
         <f>D15*E15</f>
-        <v>278832</v>
+        <v>348540</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C16" s="111"/>
       <c r="D16" s="112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" s="112">
         <f>'Оснащение и офис'!E9</f>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="F16" s="112">
         <f>D16*E16</f>
-        <v>73750</v>
+        <v>88500</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5671,7 +5671,7 @@
       <c r="E18" s="112"/>
       <c r="F18" s="112">
         <f>ROUND((F15+F16)*Сборка_мебели_проц,0)</f>
-        <v>35258</v>
+        <v>43704</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5684,7 +5684,7 @@
       <c r="E19" s="114"/>
       <c r="F19" s="114">
         <f>SUM(F15:F18)</f>
-        <v>412690</v>
+        <v>505594</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7955,7 +7955,7 @@
         <v>82</v>
       </c>
       <c r="G32" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="18">
         <v>1000000</v>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="K32" s="18">
         <f t="shared" si="26"/>
-        <v>0</v>
+        <v>1147550</v>
       </c>
       <c r="L32" s="19">
         <f t="shared" si="2"/>
@@ -7977,15 +7977,15 @@
       </c>
       <c r="M32" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2295100</v>
       </c>
       <c r="N32" s="18">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>33952.380952380954</v>
       </c>
       <c r="O32" s="18">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2329052.3809523811</v>
       </c>
       <c r="P32" s="17" t="s">
         <v>358</v>
@@ -8231,30 +8231,30 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7">
         <f>SUM(G5:G36)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H37" s="6">
         <f>SUMPRODUCT(G5:G36,H5:H36)</f>
-        <v>23600000</v>
+        <v>24600000</v>
       </c>
       <c r="I37" s="7"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6">
         <f>SUM(K5:K36)</f>
-        <v>27034580</v>
+        <v>28182130</v>
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="6">
         <f>SUM(M5:M36)</f>
-        <v>52586270</v>
+        <v>54881370</v>
       </c>
       <c r="N37" s="6">
         <f t="shared" ref="N37:O37" si="37">SUM(N5:N36)</f>
-        <v>611142.85714285716</v>
+        <v>645095.23809523811</v>
       </c>
       <c r="O37" s="6">
         <f t="shared" si="37"/>
-        <v>53197412.857142851</v>
+        <v>55526465.238095231</v>
       </c>
       <c r="P37" s="7"/>
     </row>
@@ -8277,11 +8277,11 @@
       </c>
       <c r="G39">
         <f>G37-G38</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H39" s="5">
         <f>H37-H38</f>
-        <v>8100000</v>
+        <v>9100000</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -94,6 +94,9 @@
     <definedName name="Дней_РК" localSheetId="13">#REF!</definedName>
     <definedName name="Дней_РК" localSheetId="12">#REF!</definedName>
     <definedName name="Дней_РК">Параметры!$B$21</definedName>
+    <definedName name="Долг_ЗП">Параметры!$B$55</definedName>
+    <definedName name="Долг_НДС">Параметры!$B$56</definedName>
+    <definedName name="Долг_прочие">Параметры!$B$57</definedName>
     <definedName name="Кап_ООСМС" localSheetId="8">#REF!</definedName>
     <definedName name="Кап_ООСМС" localSheetId="11">#REF!</definedName>
     <definedName name="Кап_ООСМС" localSheetId="10">#REF!</definedName>
@@ -382,7 +385,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="622">
   <si>
     <t>Статья</t>
   </si>
@@ -1453,9 +1456,6 @@
   </si>
   <si>
     <t>3. ОСНС: годовой полис на новых сотрудников</t>
-  </si>
-  <si>
-    <t>Непредвиденные расходы: резерв 10% и прочие (страхование фото- и видеооборудования, нотариус, переводы и т.п.)</t>
   </si>
   <si>
     <t>Международные и страновые проекты Фонда</t>
@@ -2103,9 +2103,6 @@
     <t>Месяц оплаты разовых (11 / 12)</t>
   </si>
   <si>
-    <t>НДС 16% на закупки, аренду, услуги и подписки (п. 5–8; аутсорс и командировки – уже с НДС, оклады, ОСНС и депозит – без НДС)</t>
-  </si>
-  <si>
     <t>Нарастающим итогом</t>
   </si>
   <si>
@@ -2251,6 +2248,33 @@
   </si>
   <si>
     <t>Итого ноябрь 2026 – февраль 2027</t>
+  </si>
+  <si>
+    <t>Задолженность Фонда на 01.11.2026 (погашение в ноябре)</t>
+  </si>
+  <si>
+    <t>Долг_ЗП</t>
+  </si>
+  <si>
+    <t>Оплата труда за июль–октябрь 2026 с налогами – в строке «Оплата труда»</t>
+  </si>
+  <si>
+    <t>Долг_НДС</t>
+  </si>
+  <si>
+    <t>Задолженность по НДС – в строке НДС</t>
+  </si>
+  <si>
+    <t>Долг_прочие</t>
+  </si>
+  <si>
+    <t>Прочая кредиторская задолженность – в строке «Резерв и прочие расходы»</t>
+  </si>
+  <si>
+    <t>НДС: 16% на закупки, аренду, услуги и подписки; расчёты с бюджетом по НДС</t>
+  </si>
+  <si>
+    <t>Резерв 10% и прочие расходы (нотариус, переводы, страхование, прочая кредиторская задолженность)</t>
   </si>
 </sst>
 </file>
@@ -2696,10 +2720,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2719,6 +2739,10 @@
     <xf numFmtId="3" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2996,7 +3020,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3004,19 +3028,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
+        <v>560</v>
+      </c>
+      <c r="C3" s="35" t="s">
         <v>561</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="D3" s="35" t="s">
         <v>562</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>563</v>
-      </c>
       <c r="E3" s="35" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,11 +3080,11 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B6" s="38">
-        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+B20</f>
-        <v>64149240</v>
+        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Долг_ЗП</f>
+        <v>56312240</v>
       </c>
       <c r="C6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=3)))+C7+C20</f>
@@ -3075,13 +3099,13 @@
         <v>34985400</v>
       </c>
       <c r="F6" s="38">
-        <f>SUM(B6:E6)</f>
-        <v>164888420</v>
+        <f t="shared" ref="F6:F20" si="0">SUM(B6:E6)</f>
+        <v>157051420</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -3097,13 +3121,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="38">
-        <f>SUM(B7:E7)</f>
+        <f t="shared" si="0"/>
         <v>9389520</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B8" s="38">
         <f>SUMPRODUCT(Аутсорс!$I$4:$I$10*((Аутсорс!$J$4:$J$10&lt;=1)+(Аутсорс!$J$4:$J$10&lt;=2)))</f>
@@ -3122,7 +3146,7 @@
         <v>6881596</v>
       </c>
       <c r="F8" s="38">
-        <f>SUM(B8:E8)</f>
+        <f t="shared" si="0"/>
         <v>27526384</v>
       </c>
     </row>
@@ -3145,7 +3169,7 @@
         <v>205000</v>
       </c>
       <c r="F9" s="38">
-        <f>SUM(B9:E9)</f>
+        <f t="shared" si="0"/>
         <v>850095.23809523811</v>
       </c>
     </row>
@@ -3170,7 +3194,7 @@
         <v>2554912.5</v>
       </c>
       <c r="F10" s="38">
-        <f>SUM(B10:E10)</f>
+        <f t="shared" si="0"/>
         <v>8312775</v>
       </c>
     </row>
@@ -3195,7 +3219,7 @@
         <v>505594</v>
       </c>
       <c r="F11" s="38">
-        <f>SUM(B11:E11)</f>
+        <f t="shared" si="0"/>
         <v>14537636.9</v>
       </c>
     </row>
@@ -3220,7 +3244,7 @@
         <v>5212743.0999999996</v>
       </c>
       <c r="F12" s="38">
-        <f>SUM(B12:E12)</f>
+        <f t="shared" si="0"/>
         <v>27467936.148387097</v>
       </c>
     </row>
@@ -3245,7 +3269,7 @@
         <v>302500</v>
       </c>
       <c r="F13" s="38">
-        <f>SUM(B13:E13)</f>
+        <f t="shared" si="0"/>
         <v>1142447</v>
       </c>
     </row>
@@ -3270,7 +3294,7 @@
         <v>1175000</v>
       </c>
       <c r="F14" s="38">
-        <f>SUM(B14:E14)</f>
+        <f t="shared" si="0"/>
         <v>4700000</v>
       </c>
     </row>
@@ -3280,7 +3304,7 @@
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)-B7</f>
-        <v>99249525.236482337</v>
+        <v>91412525.236482337</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)-C7</f>
@@ -3295,17 +3319,17 @@
         <v>51822745.600000001</v>
       </c>
       <c r="F15" s="40">
-        <f>SUM(B15:E15)</f>
-        <v>249425694.28648233</v>
+        <f t="shared" si="0"/>
+        <v>241588694.28648233</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>357</v>
+        <v>621</v>
       </c>
       <c r="B16" s="38">
-        <f>(B15-B20)*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
-        <v>6529952.5236482341</v>
+        <f>(B15-Долг_ЗП)*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")+Долг_прочие</f>
+        <v>7011952.5236482341</v>
       </c>
       <c r="C16" s="38">
         <f>(C15-C20)*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
@@ -3320,17 +3344,17 @@
         <v>5182274.5600000005</v>
       </c>
       <c r="F16" s="38">
-        <f>SUM(B16:E16)</f>
-        <v>21547569.428648233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>22029569.428648233</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>565</v>
+        <v>620</v>
       </c>
       <c r="B17" s="38">
-        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС</f>
-        <v>3661668.6741161295</v>
+        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС+Долг_НДС</f>
+        <v>11016668.674116129</v>
       </c>
       <c r="C17" s="38">
         <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59)*(1+Резерв)*НДС</f>
@@ -3345,8 +3369,8 @@
         <v>1266467.3296000001</v>
       </c>
       <c r="F17" s="38">
-        <f>SUM(B17:E17)</f>
-        <v>7564280.7589161294</v>
+        <f t="shared" si="0"/>
+        <v>14919280.75891613</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3370,7 +3394,7 @@
         <v>58271487.489600003</v>
       </c>
       <c r="F18" s="42">
-        <f>SUM(B18:E18)</f>
+        <f t="shared" si="0"/>
         <v>278537544.47404671</v>
       </c>
     </row>
@@ -3395,15 +3419,16 @@
         <v>29078106.666666668</v>
       </c>
       <c r="F19" s="40">
-        <f>SUM(B19:E19)</f>
+        <f t="shared" si="0"/>
         <v>116312426.66666667</v>
       </c>
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B20" s="40">
+        <f>Долг_ЗП+Долг_НДС+Долг_прочие</f>
         <v>37450000</v>
       </c>
       <c r="C20" s="40">
@@ -3416,13 +3441,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="40">
-        <f>SUM(B20:E20)</f>
+        <f t="shared" si="0"/>
         <v>37450000</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3447,7 +3472,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B23" s="44">
         <f>B21</f>
@@ -3469,7 +3494,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="106" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -3481,7 +3506,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -3527,45 +3552,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>416</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3577,13 +3602,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>417</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>418</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3598,13 +3623,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3620,13 +3645,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3641,13 +3666,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B8" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>421</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>422</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -3662,13 +3687,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B9" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="C9" s="55" t="s">
         <v>423</v>
-      </c>
-      <c r="C9" s="55" t="s">
-        <v>424</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -3683,13 +3708,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -3705,10 +3730,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -3723,13 +3748,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -3744,13 +3769,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
+        <v>426</v>
+      </c>
+      <c r="B13" s="75" t="s">
         <v>427</v>
       </c>
-      <c r="B13" s="75" t="s">
-        <v>428</v>
-      </c>
       <c r="C13" s="76" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -3766,7 +3791,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -3779,7 +3804,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3835,45 +3860,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>429</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>428</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3885,13 +3910,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" s="57" t="s">
+        <v>429</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>430</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>431</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3906,13 +3931,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>432</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>433</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3928,13 +3953,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3950,7 +3975,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -3963,7 +3988,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -4019,45 +4044,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>435</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>434</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4069,13 +4094,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -4090,13 +4115,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4112,13 +4137,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -4133,13 +4158,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -4154,13 +4179,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -4175,13 +4200,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -4196,13 +4221,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -4219,7 +4244,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -4232,7 +4257,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -4285,45 +4310,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>443</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4335,13 +4360,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4356,13 +4381,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4379,7 +4404,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -4392,7 +4417,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -4448,45 +4473,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>446</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>445</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4498,13 +4523,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4520,7 +4545,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -4534,7 +4559,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4926,7 +4951,7 @@
         <v>188</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4943,7 +4968,7 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5366,404 +5391,404 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="107" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="108" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="108" t="s">
+        <v>571</v>
+      </c>
+      <c r="C3" s="108" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="110" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="110" t="s">
+      <c r="D3" s="108" t="s">
         <v>573</v>
       </c>
-      <c r="C3" s="110" t="s">
+      <c r="E3" s="108" t="s">
         <v>574</v>
       </c>
-      <c r="D3" s="110" t="s">
+      <c r="F3" s="108" t="s">
         <v>575</v>
       </c>
-      <c r="E3" s="110" t="s">
+    </row>
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="109" t="s">
         <v>576</v>
       </c>
-      <c r="F3" s="110" t="s">
+      <c r="B4" s="109" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="111" t="s">
+      <c r="C4" s="109" t="s">
         <v>578</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="D4" s="110">
+        <v>1300000</v>
+      </c>
+      <c r="E4" s="110">
+        <f t="shared" ref="E4:E10" si="0">ROUND(Ставка_СН*D4*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D4+Ставка_СО*MIN(D4*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D4,Кап_ООСМС*МЗП),0)</f>
+        <v>182890</v>
+      </c>
+      <c r="F4" s="110">
+        <f t="shared" ref="F4:F10" si="1">D4+E4</f>
+        <v>1482890</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="109" t="s">
+        <v>241</v>
+      </c>
+      <c r="B5" s="109" t="s">
+        <v>577</v>
+      </c>
+      <c r="C5" s="109" t="s">
         <v>579</v>
       </c>
-      <c r="C4" s="111" t="s">
+      <c r="D5" s="110">
+        <v>1000000</v>
+      </c>
+      <c r="E5" s="110">
+        <f t="shared" si="0"/>
+        <v>147550</v>
+      </c>
+      <c r="F5" s="110">
+        <f t="shared" si="1"/>
+        <v>1147550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="109" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="109" t="s">
+        <v>577</v>
+      </c>
+      <c r="C6" s="109" t="s">
         <v>580</v>
       </c>
-      <c r="D4" s="112">
-        <v>1300000</v>
-      </c>
-      <c r="E4" s="112">
-        <f>ROUND(Ставка_СН*D4*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D4+Ставка_СО*MIN(D4*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D4,Кап_ООСМС*МЗП),0)</f>
-        <v>182890</v>
-      </c>
-      <c r="F4" s="112">
-        <f>D4+E4</f>
-        <v>1482890</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
-        <v>241</v>
-      </c>
-      <c r="B5" s="111" t="s">
-        <v>579</v>
-      </c>
-      <c r="C5" s="111" t="s">
+      <c r="D6" s="110">
+        <v>700000</v>
+      </c>
+      <c r="E6" s="110">
+        <f t="shared" si="0"/>
+        <v>112210</v>
+      </c>
+      <c r="F6" s="110">
+        <f t="shared" si="1"/>
+        <v>812210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="109" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" s="109" t="s">
+        <v>577</v>
+      </c>
+      <c r="C7" s="109" t="s">
         <v>581</v>
       </c>
-      <c r="D5" s="112">
-        <v>1000000</v>
-      </c>
-      <c r="E5" s="112">
-        <f>ROUND(Ставка_СН*D5*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D5+Ставка_СО*MIN(D5*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D5,Кап_ООСМС*МЗП),0)</f>
-        <v>147550</v>
-      </c>
-      <c r="F5" s="112">
-        <f>D5+E5</f>
-        <v>1147550</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="D7" s="110">
+        <v>700000</v>
+      </c>
+      <c r="E7" s="110">
+        <f t="shared" si="0"/>
+        <v>112210</v>
+      </c>
+      <c r="F7" s="110">
+        <f t="shared" si="1"/>
+        <v>812210</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="109" t="s">
         <v>243</v>
       </c>
-      <c r="B6" s="111" t="s">
-        <v>579</v>
-      </c>
-      <c r="C6" s="111" t="s">
+      <c r="B8" s="109" t="s">
+        <v>577</v>
+      </c>
+      <c r="C8" s="109" t="s">
         <v>582</v>
       </c>
-      <c r="D6" s="112">
+      <c r="D8" s="110">
         <v>700000</v>
       </c>
-      <c r="E6" s="112">
-        <f>ROUND(Ставка_СН*D6*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D6+Ставка_СО*MIN(D6*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D6,Кап_ООСМС*МЗП),0)</f>
+      <c r="E8" s="110">
+        <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="F6" s="112">
-        <f>D6+E6</f>
+      <c r="F8" s="110">
+        <f t="shared" si="1"/>
         <v>812210</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="B7" s="111" t="s">
-        <v>579</v>
-      </c>
-      <c r="C7" s="111" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="109" t="s">
         <v>583</v>
       </c>
-      <c r="D7" s="112">
+      <c r="B9" s="109" t="s">
+        <v>584</v>
+      </c>
+      <c r="C9" s="109" t="s">
+        <v>585</v>
+      </c>
+      <c r="D9" s="110">
         <v>700000</v>
       </c>
-      <c r="E7" s="112">
-        <f>ROUND(Ставка_СН*D7*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D7+Ставка_СО*MIN(D7*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D7,Кап_ООСМС*МЗП),0)</f>
+      <c r="E9" s="110">
+        <f t="shared" si="0"/>
         <v>112210</v>
       </c>
-      <c r="F7" s="112">
-        <f>D7+E7</f>
+      <c r="F9" s="110">
+        <f t="shared" si="1"/>
         <v>812210</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="111" t="s">
-        <v>243</v>
-      </c>
-      <c r="B8" s="111" t="s">
-        <v>579</v>
-      </c>
-      <c r="C8" s="111" t="s">
-        <v>584</v>
-      </c>
-      <c r="D8" s="112">
-        <v>700000</v>
-      </c>
-      <c r="E8" s="112">
-        <f>ROUND(Ставка_СН*D8*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D8+Ставка_СО*MIN(D8*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D8,Кап_ООСМС*МЗП),0)</f>
-        <v>112210</v>
-      </c>
-      <c r="F8" s="112">
-        <f>D8+E8</f>
-        <v>812210</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="111" t="s">
-        <v>585</v>
-      </c>
-      <c r="B9" s="111" t="s">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="109" t="s">
         <v>586</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="B10" s="109" t="s">
         <v>587</v>
       </c>
-      <c r="D9" s="112">
-        <v>700000</v>
-      </c>
-      <c r="E9" s="112">
-        <f>ROUND(Ставка_СН*D9*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D9+Ставка_СО*MIN(D9*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D9,Кап_ООСМС*МЗП),0)</f>
-        <v>112210</v>
-      </c>
-      <c r="F9" s="112">
-        <f>D9+E9</f>
-        <v>812210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="111" t="s">
+      <c r="C10" s="109" t="s">
         <v>588</v>
       </c>
-      <c r="B10" s="111" t="s">
+      <c r="D10" s="110">
+        <v>800000</v>
+      </c>
+      <c r="E10" s="110">
+        <f t="shared" si="0"/>
+        <v>123990</v>
+      </c>
+      <c r="F10" s="110">
+        <f t="shared" si="1"/>
+        <v>923990</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="111" t="s">
         <v>589</v>
       </c>
-      <c r="C10" s="111" t="s">
-        <v>590</v>
-      </c>
-      <c r="D10" s="112">
-        <v>800000</v>
-      </c>
-      <c r="E10" s="112">
-        <f>ROUND(Ставка_СН*D10*(1-Ставка_ОПВ-Ставка_ВОСМС)+Ставка_ОПВР*D10+Ставка_СО*MIN(D10*(1-Ставка_ОПВ),Кап_СО*МЗП)+Ставка_ООСМС*MIN(D10,Кап_ООСМС*МЗП),0)</f>
-        <v>123990</v>
-      </c>
-      <c r="F10" s="112">
-        <f>D10+E10</f>
-        <v>923990</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="113" t="s">
-        <v>591</v>
-      </c>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="114">
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="112">
         <f>SUM(D4:D10)</f>
         <v>5900000</v>
       </c>
-      <c r="E11" s="114">
+      <c r="E11" s="112">
         <f>SUM(E4:E10)</f>
         <v>903270</v>
       </c>
-      <c r="F11" s="114">
+      <c r="F11" s="112">
         <f>SUM(F4:F10)</f>
         <v>6803270</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="111"/>
-      <c r="B12" s="111"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
+      <c r="A12" s="109"/>
+      <c r="B12" s="109"/>
+      <c r="C12" s="109"/>
+      <c r="D12" s="110"/>
+      <c r="E12" s="110"/>
+      <c r="F12" s="110"/>
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="113" t="s">
+      <c r="A13" s="111" t="s">
+        <v>590</v>
+      </c>
+      <c r="B13" s="109"/>
+      <c r="C13" s="109"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="108" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="108" t="s">
+        <v>591</v>
+      </c>
+      <c r="C14" s="108"/>
+      <c r="D14" s="113" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="113" t="s">
         <v>592</v>
       </c>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="112"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="112"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="110" t="s">
-        <v>175</v>
-      </c>
-      <c r="B14" s="110" t="s">
+      <c r="F14" s="113" t="s">
         <v>593</v>
       </c>
-      <c r="C14" s="110"/>
-      <c r="D14" s="115" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="115" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="109" t="s">
         <v>594</v>
       </c>
-      <c r="F14" s="115" t="s">
+      <c r="B15" s="109" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
-        <v>596</v>
-      </c>
-      <c r="B15" s="111" t="s">
-        <v>597</v>
-      </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="112">
+      <c r="C15" s="109"/>
+      <c r="D15" s="110">
         <v>5</v>
       </c>
-      <c r="E15" s="112">
+      <c r="E15" s="110">
         <f>'Оснащение и офис'!E8</f>
         <v>69708</v>
       </c>
-      <c r="F15" s="112">
+      <c r="F15" s="110">
         <f>D15*E15</f>
         <v>348540</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="111" t="s">
-        <v>598</v>
-      </c>
-      <c r="B16" s="111" t="s">
-        <v>599</v>
-      </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="112">
+      <c r="A16" s="109" t="s">
+        <v>596</v>
+      </c>
+      <c r="B16" s="109" t="s">
+        <v>597</v>
+      </c>
+      <c r="C16" s="109"/>
+      <c r="D16" s="110">
         <v>6</v>
       </c>
-      <c r="E16" s="112">
+      <c r="E16" s="110">
         <f>'Оснащение и офис'!E9</f>
         <v>14750</v>
       </c>
-      <c r="F16" s="112">
+      <c r="F16" s="110">
         <f>D16*E16</f>
         <v>88500</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="111" t="s">
-        <v>600</v>
-      </c>
-      <c r="B17" s="111" t="s">
-        <v>601</v>
-      </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="112">
+      <c r="A17" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="B17" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="C17" s="109"/>
+      <c r="D17" s="110">
         <v>7</v>
       </c>
-      <c r="E17" s="112">
+      <c r="E17" s="110">
         <f>'Оснащение и офис'!E37</f>
         <v>3550</v>
       </c>
-      <c r="F17" s="112">
+      <c r="F17" s="110">
         <f>D17*E17</f>
         <v>24850</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="111" t="s">
+      <c r="A18" s="109" t="s">
         <v>214</v>
       </c>
-      <c r="B18" s="111" t="s">
-        <v>602</v>
-      </c>
-      <c r="C18" s="111"/>
-      <c r="D18" s="112"/>
-      <c r="E18" s="112"/>
-      <c r="F18" s="112">
+      <c r="B18" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="C18" s="109"/>
+      <c r="D18" s="110"/>
+      <c r="E18" s="110"/>
+      <c r="F18" s="110">
         <f>ROUND((F15+F16)*Сборка_мебели_проц,0)</f>
         <v>43704</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="113" t="s">
-        <v>603</v>
-      </c>
-      <c r="B19" s="113"/>
-      <c r="C19" s="113"/>
-      <c r="D19" s="114"/>
-      <c r="E19" s="114"/>
-      <c r="F19" s="114">
+      <c r="A19" s="111" t="s">
+        <v>601</v>
+      </c>
+      <c r="B19" s="111"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="112"/>
+      <c r="E19" s="112"/>
+      <c r="F19" s="112">
         <f>SUM(F15:F18)</f>
         <v>505594</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="111"/>
-      <c r="B20" s="111"/>
-      <c r="C20" s="111"/>
-      <c r="D20" s="112"/>
-      <c r="E20" s="112"/>
-      <c r="F20" s="112"/>
+      <c r="A20" s="109"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="109"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="113" t="s">
-        <v>604</v>
-      </c>
-      <c r="B21" s="111"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="112"/>
-      <c r="E21" s="112"/>
-      <c r="F21" s="112"/>
+      <c r="A21" s="111" t="s">
+        <v>602</v>
+      </c>
+      <c r="B21" s="109"/>
+      <c r="C21" s="109"/>
+      <c r="D21" s="110"/>
+      <c r="E21" s="110"/>
+      <c r="F21" s="110"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="111" t="s">
-        <v>605</v>
-      </c>
-      <c r="B22" s="111"/>
-      <c r="C22" s="111"/>
-      <c r="D22" s="112">
+      <c r="A22" s="109" t="s">
+        <v>603</v>
+      </c>
+      <c r="B22" s="109"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="110">
         <v>7</v>
       </c>
-      <c r="E22" s="112">
+      <c r="E22" s="110">
         <f>'Оснащение и офис'!E68</f>
         <v>7000</v>
       </c>
-      <c r="F22" s="112">
+      <c r="F22" s="110">
         <f>D22*E22</f>
         <v>49000</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="111" t="s">
-        <v>606</v>
-      </c>
-      <c r="B23" s="111" t="s">
-        <v>607</v>
-      </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="112">
+      <c r="A23" s="109" t="s">
+        <v>604</v>
+      </c>
+      <c r="B23" s="109" t="s">
+        <v>605</v>
+      </c>
+      <c r="C23" s="109"/>
+      <c r="D23" s="110"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110">
         <f>ROUND(0.29%*12*D11,-3)</f>
         <v>205000</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="111" t="s">
-        <v>608</v>
-      </c>
-      <c r="B24" s="111" t="s">
-        <v>609</v>
-      </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="112"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="112">
+      <c r="A24" s="109" t="s">
+        <v>606</v>
+      </c>
+      <c r="B24" s="109" t="s">
+        <v>607</v>
+      </c>
+      <c r="C24" s="109"/>
+      <c r="D24" s="110"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110">
         <f>5*6/12*Поездка_РК+1*(3/12*Поездка_РК+3*Поездка_местн)</f>
         <v>596062.5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="111" t="s">
-        <v>610</v>
-      </c>
-      <c r="B25" s="111" t="s">
-        <v>611</v>
-      </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112">
+      <c r="A25" s="109" t="s">
+        <v>608</v>
+      </c>
+      <c r="B25" s="109" t="s">
+        <v>609</v>
+      </c>
+      <c r="C25" s="109"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110">
         <f>Проекты!G13/3</f>
         <v>29078106.666666668</v>
       </c>
@@ -5776,7 +5801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -5933,7 +5958,7 @@
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6218,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -6292,7 +6317,45 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>388</v>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="7" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>614</v>
+      </c>
+      <c r="B55" s="5">
+        <v>29613000</v>
+      </c>
+      <c r="C55" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>616</v>
+      </c>
+      <c r="B56" s="5">
+        <v>7355000</v>
+      </c>
+      <c r="C56" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>618</v>
+      </c>
+      <c r="B57" s="5">
+        <v>482000</v>
+      </c>
+      <c r="C57" t="s">
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -6362,7 +6425,7 @@
         <v>74</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>76</v>
@@ -6377,7 +6440,7 @@
         <v>316</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -6433,7 +6496,7 @@
         <v>3636460</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q5" s="89"/>
     </row>
@@ -6445,7 +6508,7 @@
         <v>263</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>81</v>
@@ -6490,7 +6553,7 @@
         <v>3189340</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="Q6" s="89"/>
     </row>
@@ -6547,7 +6610,7 @@
         <v>3189340</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="Q7" s="89"/>
     </row>
@@ -6559,7 +6622,7 @@
         <v>207</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>81</v>
@@ -6604,7 +6667,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q8" s="89">
         <v>1</v>
@@ -6621,7 +6684,7 @@
         <v>237</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -6663,7 +6726,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q9" s="89"/>
     </row>
@@ -6675,7 +6738,7 @@
         <v>236</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D10" s="17" t="s">
         <v>239</v>
@@ -6720,7 +6783,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Q10" s="89">
         <v>1</v>
@@ -6734,7 +6797,7 @@
         <v>236</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>239</v>
@@ -6779,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q11" s="89"/>
     </row>
@@ -6950,7 +7013,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="Q14" s="89">
         <v>1</v>
@@ -7009,7 +7072,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q15" s="89">
         <v>1</v>
@@ -7068,7 +7131,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q16" s="89">
         <v>1</v>
@@ -7127,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -7184,7 +7247,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -7241,7 +7304,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="Q19" s="89"/>
     </row>
@@ -7256,7 +7319,7 @@
         <v>237</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -7298,7 +7361,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Q20" s="89">
         <v>1</v>
@@ -7372,7 +7435,7 @@
         <v>247</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -7414,7 +7477,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q22" s="89"/>
     </row>
@@ -7471,7 +7534,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q23" s="89">
         <v>1</v>
@@ -7599,7 +7662,7 @@
         <v>246</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>208</v>
@@ -7644,7 +7707,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="Q26" s="89">
         <v>1</v>
@@ -7703,7 +7766,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="Q27" s="89"/>
     </row>
@@ -7940,13 +8003,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>79</v>
@@ -7988,7 +8051,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q32" s="89"/>
     </row>
@@ -7997,13 +8060,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>79</v>
@@ -8045,7 +8108,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q33" s="89"/>
     </row>
@@ -8054,13 +8117,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>79</v>
@@ -8102,7 +8165,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q34" s="89"/>
     </row>
@@ -8286,12 +8349,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -8300,7 +8363,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -8309,7 +8372,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -8318,7 +8381,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -8369,10 +8432,10 @@
         <v>275</v>
       </c>
       <c r="F3" s="103" t="s">
+        <v>517</v>
+      </c>
+      <c r="G3" s="103" t="s">
         <v>518</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>519</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>276</v>
@@ -8395,7 +8458,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>206</v>
@@ -8439,7 +8502,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>206</v>
@@ -8615,13 +8678,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="C9" s="27" t="s">
         <v>378</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>379</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>380</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -8734,7 +8797,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -8756,12 +8819,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8772,48 +8835,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="95" t="s">
         <v>500</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="C7" s="95" t="s">
         <v>501</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="D7" s="95" t="s">
         <v>502</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="E7" s="95" t="s">
         <v>503</v>
       </c>
-      <c r="E7" s="95" t="s">
+      <c r="F7" s="95" t="s">
         <v>504</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>505</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8934,48 +8997,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -8985,7 +9048,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -8995,7 +9058,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -9005,7 +9068,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -9015,7 +9078,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -9025,7 +9088,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -9074,7 +9137,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>90</v>
@@ -9154,7 +9217,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -9177,7 +9240,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -9223,7 +9286,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -9321,16 +9384,16 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9356,7 +9419,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I57" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -9446,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -9473,7 +9536,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -9492,7 +9555,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -9519,7 +9582,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -9538,7 +9601,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9" si="4">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
@@ -9565,7 +9628,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -9584,7 +9647,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10" si="5">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
@@ -9611,7 +9674,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -9630,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11" si="6">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
@@ -9657,7 +9720,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -9676,7 +9739,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -9703,7 +9766,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -9722,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
@@ -9749,7 +9812,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -9768,7 +9831,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
@@ -9795,7 +9858,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9814,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" ref="I15" si="7">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
@@ -9841,7 +9904,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9860,7 +9923,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" ref="I16:I21" si="8">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
@@ -9887,7 +9950,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9906,7 +9969,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="8"/>
@@ -9933,7 +9996,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -9952,7 +10015,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="8"/>
@@ -9979,7 +10042,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -9998,7 +10061,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="8"/>
@@ -10025,7 +10088,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -10044,7 +10107,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="8"/>
@@ -10071,7 +10134,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -10090,7 +10153,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="8"/>
@@ -10203,7 +10266,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -10221,7 +10284,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -10339,7 +10402,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -10358,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
@@ -10803,7 +10866,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
@@ -11014,7 +11077,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -11033,7 +11096,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
@@ -11106,7 +11169,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -11125,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
@@ -11152,7 +11215,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -11171,7 +11234,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
@@ -11198,7 +11261,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -11216,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
@@ -11350,7 +11413,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="0"/>
@@ -11466,7 +11529,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -11485,7 +11548,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" ref="I52:I54" si="14">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
@@ -11512,7 +11575,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -11531,7 +11594,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="14"/>
@@ -11558,7 +11621,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -11577,7 +11640,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="14"/>
@@ -11841,7 +11904,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="15"/>
@@ -11948,10 +12011,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C63" s="105" t="s">
         <v>558</v>
-      </c>
-      <c r="C63" s="105" t="s">
-        <v>559</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -11967,7 +12030,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
@@ -12291,7 +12354,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -12310,7 +12373,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="15"/>
@@ -12337,10 +12400,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C72" s="102" t="s">
         <v>515</v>
-      </c>
-      <c r="C72" s="102" t="s">
-        <v>516</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -12355,7 +12418,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
@@ -12496,7 +12559,7 @@
         <v>132</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -12514,7 +12577,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="15"/>
@@ -12630,13 +12693,13 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
+        <v>560</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>561</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>562</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
@@ -12644,7 +12707,7 @@
         <v>273</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C5" t="s">
         <v>234</v>
@@ -12676,7 +12739,7 @@
         <v>273</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C6" t="s">
         <v>234</v>
@@ -12740,7 +12803,7 @@
         <v>273</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C8" t="s">
         <v>234</v>
@@ -12772,7 +12835,7 @@
         <v>273</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C9" t="s">
         <v>234</v>
@@ -12804,7 +12867,7 @@
         <v>273</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C10" t="s">
         <v>234</v>
@@ -12895,45 +12958,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107" t="s">
-        <v>393</v>
-      </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="108"/>
+      <c r="A1" s="114" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
     </row>
     <row r="3" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A3" s="47" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C3" s="49" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="D3" s="49" t="s">
         <v>395</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>396</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="F3" s="50" t="s">
         <v>397</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -12945,13 +13008,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="54" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="C5" s="55" t="s">
         <v>401</v>
-      </c>
-      <c r="C5" s="55" t="s">
-        <v>402</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -12966,13 +13029,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
+        <v>402</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>403</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="C6" s="55" t="s">
         <v>404</v>
-      </c>
-      <c r="C6" s="55" t="s">
-        <v>405</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -12988,13 +13051,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>406</v>
       </c>
-      <c r="B7" s="57" t="s">
-        <v>407</v>
-      </c>
       <c r="C7" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -13009,13 +13072,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
+        <v>407</v>
+      </c>
+      <c r="B8" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="B8" s="57" t="s">
-        <v>409</v>
-      </c>
       <c r="C8" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -13030,13 +13093,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
+        <v>409</v>
+      </c>
+      <c r="B9" s="57" t="s">
         <v>410</v>
       </c>
-      <c r="B9" s="57" t="s">
-        <v>411</v>
-      </c>
       <c r="C9" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -13051,13 +13114,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="57" t="s">
         <v>412</v>
       </c>
-      <c r="B10" s="57" t="s">
-        <v>413</v>
-      </c>
       <c r="C10" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -13073,7 +13136,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -13086,7 +13149,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -385,7 +385,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="619">
   <si>
     <t>Статья</t>
   </si>
@@ -777,15 +777,9 @@
     <t>Полиграфия и брендированная продукция</t>
   </si>
   <si>
-    <t>год</t>
-  </si>
-  <si>
     <t>Фотобанк, музыка (подписки)</t>
   </si>
   <si>
-    <t>Прочие</t>
-  </si>
-  <si>
     <t>Смета фото- и видеооборудования, ₸</t>
   </si>
   <si>
@@ -1356,9 +1350,6 @@
     <t>Аутсорс-услуги: расчёт на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
-    <t>Оснащение, офис, цифровые инструменты, медиа и прочие расходы на октябрь–декабрь 2026 года, ₸</t>
-  </si>
-  <si>
     <t>Тип: разово – в месяц старта; мес – ежемесячно с месяца старта; год – годовая сумма × 3/12.</t>
   </si>
   <si>
@@ -1420,12 +1411,6 @@
   </si>
   <si>
     <t>новые сотрудники 2026 года</t>
-  </si>
-  <si>
-    <t>Страхование фото- и видеооборудования</t>
-  </si>
-  <si>
-    <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские</t>
   </si>
   <si>
     <t>Разово при открытии офиса</t>
@@ -2274,7 +2259,13 @@
     <t>НДС: 16% на закупки, аренду, услуги и подписки; расчёты с бюджетом по НДС</t>
   </si>
   <si>
-    <t>Резерв 10% и прочие расходы (нотариус, переводы, страхование, прочая кредиторская задолженность)</t>
+    <t>Оснащение, офис, цифровые инструменты и медиа на октябрь–декабрь 2026 года, ₸</t>
+  </si>
+  <si>
+    <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские, нотариус и услуги МФЦА</t>
+  </si>
+  <si>
+    <t>Резерв 10% и прочие расходы (прочая кредиторская задолженность)</t>
   </si>
 </sst>
 </file>
@@ -3020,7 +3011,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3028,24 +3019,24 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="D3" s="35" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="E3" s="35" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="36" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B4" s="37">
         <f>SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$G$5:$G$36*(Штат!$I$5:$I$36&lt;=2))</f>
@@ -3067,7 +3058,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
@@ -3080,7 +3071,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="B6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Долг_ЗП</f>
@@ -3105,7 +3096,7 @@
     </row>
     <row r="7" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -3127,7 +3118,7 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="B8" s="38">
         <f>SUMPRODUCT(Аутсорс!$I$4:$I$10*((Аутсорс!$J$4:$J$10&lt;=1)+(Аутсорс!$J$4:$J$10&lt;=2)))</f>
@@ -3152,7 +3143,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B9" s="38">
         <f>Штат!$N$37</f>
@@ -3175,7 +3166,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B10" s="38">
         <f>Командировки!$G$12/2</f>
@@ -3200,7 +3191,7 @@
     </row>
     <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="36" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B11" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Оснащение")</f>
@@ -3225,11 +3216,11 @@
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>346</v>
+        <v>617</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
-        <v>11829706.848387096</v>
+        <v>12179706.848387096</v>
       </c>
       <c r="C12" s="38">
         <f>SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3245,12 +3236,12 @@
       </c>
       <c r="F12" s="38">
         <f t="shared" si="0"/>
-        <v>27467936.148387097</v>
+        <v>27817936.148387097</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B13" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Цифровые")</f>
@@ -3275,7 +3266,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B14" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Медиа")</f>
@@ -3300,11 +3291,11 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="39" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)-B7</f>
-        <v>91412525.236482337</v>
+        <v>91762525.236482337</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)-C7</f>
@@ -3320,23 +3311,23 @@
       </c>
       <c r="F15" s="40">
         <f t="shared" si="0"/>
-        <v>241588694.28648233</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>241938694.28648233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B16" s="38">
-        <f>(B15-Долг_ЗП)*Резерв+SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")+Долг_прочие</f>
-        <v>7011952.5236482341</v>
+        <f>(B15-Долг_ЗП-'Оснащение и офис'!$J$76)*Резерв+Долг_прочие</f>
+        <v>6661952.5236482341</v>
       </c>
       <c r="C16" s="38">
-        <f>(C15-C20)*Резерв+SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
+        <f>(C15-C20-'Оснащение и офис'!$K$76)*Резерв</f>
         <v>5468960.4350000005</v>
       </c>
       <c r="D16" s="38">
-        <f>(D15-D20)*Резерв+SUMIFS('Оснащение и офис'!$L$5:$L$77,'Оснащение и офис'!$A$5:$A$77,"Прочие")</f>
+        <f>(D15-D20-'Оснащение и офис'!$L$76)*Резерв</f>
         <v>4366381.91</v>
       </c>
       <c r="E16" s="38">
@@ -3345,23 +3336,23 @@
       </c>
       <c r="F16" s="38">
         <f t="shared" si="0"/>
-        <v>22029569.428648233</v>
+        <v>21679569.428648233</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="B17" s="38">
-        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59)*(1+Резерв)*НДС+Долг_НДС</f>
+        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС</f>
         <v>11016668.674116129</v>
       </c>
       <c r="C17" s="38">
-        <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59)*(1+Резерв)*НДС</f>
+        <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59-'Оснащение и офис'!$K$76)*(1+Резерв)*НДС</f>
         <v>1467285.9696000002</v>
       </c>
       <c r="D17" s="38">
-        <f>((D11+D12+D13+D14)-'Оснащение и офис'!$L$59)*(1+Резерв)*НДС</f>
+        <f>((D11+D12+D13+D14)-'Оснащение и офис'!$L$59-'Оснащение и офис'!$L$76)*(1+Резерв)*НДС</f>
         <v>1168858.7856000001</v>
       </c>
       <c r="E17" s="38">
@@ -3375,7 +3366,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
@@ -3400,7 +3391,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="39" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B19" s="40">
         <f>Проекты!$H$13</f>
@@ -3425,7 +3416,7 @@
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B20" s="40">
         <f>Долг_ЗП+Долг_НДС+Долг_прочие</f>
@@ -3447,7 +3438,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3472,7 +3463,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B23" s="44">
         <f>B21</f>
@@ -3494,7 +3485,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="106" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -3506,7 +3497,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -3553,7 +3544,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -3572,25 +3563,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3602,13 +3593,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -3623,13 +3614,13 @@
     </row>
     <row r="6" spans="1:12" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3645,13 +3636,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3666,13 +3657,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D8" s="55">
         <v>1</v>
@@ -3687,13 +3678,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D9" s="74">
         <v>100</v>
@@ -3708,13 +3699,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D10" s="74">
         <v>100</v>
@@ -3730,10 +3721,10 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="57" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D11" s="74">
         <v>1</v>
@@ -3748,13 +3739,13 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B12" s="57" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C12" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D12" s="55">
         <v>4</v>
@@ -3769,13 +3760,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B13" s="75" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C13" s="76" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D13" s="76">
         <v>1</v>
@@ -3791,7 +3782,7 @@
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="51"/>
       <c r="B14" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C14" s="49"/>
       <c r="D14" s="55"/>
@@ -3804,7 +3795,7 @@
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="51"/>
       <c r="B15" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C15" s="61"/>
       <c r="D15" s="61"/>
@@ -3861,7 +3852,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -3880,25 +3871,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -3910,13 +3901,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D5" s="55">
         <v>4</v>
@@ -3931,13 +3922,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -3953,13 +3944,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -3975,7 +3966,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C8" s="49"/>
       <c r="D8" s="55"/>
@@ -3988,7 +3979,7 @@
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51"/>
       <c r="B9" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C9" s="61"/>
       <c r="D9" s="61"/>
@@ -4045,7 +4036,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -4064,25 +4055,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4094,13 +4085,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D5" s="55">
         <v>6</v>
@@ -4115,13 +4106,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4137,13 +4128,13 @@
     </row>
     <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D7" s="55">
         <v>1</v>
@@ -4158,13 +4149,13 @@
     </row>
     <row r="8" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D8" s="55">
         <v>9</v>
@@ -4179,13 +4170,13 @@
     </row>
     <row r="9" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D9" s="74">
         <v>32</v>
@@ -4200,13 +4191,13 @@
     </row>
     <row r="10" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D10" s="55">
         <v>3</v>
@@ -4221,13 +4212,13 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B11" s="57" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C11" s="55" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="D11" s="55">
         <v>3</v>
@@ -4244,7 +4235,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C12" s="49"/>
       <c r="D12" s="55"/>
@@ -4257,7 +4248,7 @@
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="51"/>
       <c r="B13" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C13" s="61"/>
       <c r="D13" s="61"/>
@@ -4311,7 +4302,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -4330,25 +4321,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4360,13 +4351,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4381,13 +4372,13 @@
     </row>
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D6" s="55">
         <v>1</v>
@@ -4404,7 +4395,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C7" s="49"/>
       <c r="D7" s="55"/>
@@ -4417,7 +4408,7 @@
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51"/>
       <c r="B8" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -4474,7 +4465,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -4493,25 +4484,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -4523,13 +4514,13 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="57" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D5" s="55">
         <v>1</v>
@@ -4545,7 +4536,7 @@
     <row r="6" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51"/>
       <c r="B6" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="55"/>
@@ -4559,7 +4550,7 @@
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51"/>
       <c r="B7" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C7" s="61"/>
       <c r="D7" s="61"/>
@@ -4617,27 +4608,27 @@
   <sheetData>
     <row r="1" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>93</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>96</v>
@@ -4645,13 +4636,13 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" t="s">
         <v>178</v>
-      </c>
-      <c r="B5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C5" t="s">
-        <v>180</v>
       </c>
       <c r="D5" s="13">
         <v>3.5</v>
@@ -4664,18 +4655,18 @@
         <v>10500</v>
       </c>
       <c r="G5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C6" t="s">
         <v>178</v>
-      </c>
-      <c r="B6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C6" t="s">
-        <v>180</v>
       </c>
       <c r="D6" s="13">
         <v>0.25</v>
@@ -4688,18 +4679,18 @@
         <v>1625</v>
       </c>
       <c r="G6" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D7" s="13">
         <v>0.5</v>
@@ -4712,15 +4703,15 @@
         <v>3000</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
         <v>103</v>
@@ -4736,15 +4727,15 @@
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
@@ -4760,15 +4751,15 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C10" t="s">
         <v>103</v>
@@ -4784,12 +4775,12 @@
         <v>9000</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D11" s="32"/>
       <c r="E11" s="6"/>
@@ -4800,7 +4791,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -4809,16 +4800,16 @@
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C14" t="s">
         <v>103</v>
@@ -4834,15 +4825,15 @@
         <v>7500</v>
       </c>
       <c r="G14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
@@ -4856,15 +4847,15 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C16" t="s">
         <v>103</v>
@@ -4878,15 +4869,15 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C17" t="s">
         <v>103</v>
@@ -4902,10 +4893,10 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B18" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -4919,15 +4910,15 @@
         <v>0</v>
       </c>
       <c r="G18" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s">
         <v>103</v>
@@ -4943,15 +4934,15 @@
         <v>8000</v>
       </c>
       <c r="G19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="104" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="104" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4968,13 +4959,13 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
       <c r="B21" s="7" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="32"/>
@@ -5010,12 +5001,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5023,13 +5014,13 @@
         <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>71</v>
@@ -5038,12 +5029,12 @@
         <v>94</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -5057,13 +5048,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>5659</v>
       </c>
       <c r="D6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5081,13 +5072,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>2584</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5105,13 +5096,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8">
         <v>6218</v>
       </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -5129,13 +5120,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C9">
         <v>4240</v>
       </c>
       <c r="D9" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5153,13 +5144,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C10">
         <v>6976</v>
       </c>
       <c r="D10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5177,13 +5168,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C11">
         <v>3288</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5201,13 +5192,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C12">
         <v>1756</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5223,7 +5214,7 @@
     <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -5240,7 +5231,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -5254,10 +5245,10 @@
         <v>2.1</v>
       </c>
       <c r="B16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5273,7 +5264,7 @@
     <row r="17" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7"/>
       <c r="B17" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -5290,7 +5281,7 @@
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -5304,10 +5295,10 @@
         <v>3.3</v>
       </c>
       <c r="B20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5325,10 +5316,10 @@
         <v>3.4</v>
       </c>
       <c r="B21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E21">
         <v>2</v>
@@ -5344,7 +5335,7 @@
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7"/>
       <c r="B22" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -5362,7 +5353,7 @@
     <row r="24" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -5392,7 +5383,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5400,30 +5391,30 @@
         <v>67</v>
       </c>
       <c r="B3" s="108" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C3" s="108" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="D3" s="108" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E3" s="108" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F3" s="108" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="B4" s="109" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C4" s="109" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="D4" s="110">
         <v>1300000</v>
@@ -5439,13 +5430,13 @@
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="109" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="D5" s="110">
         <v>1000000</v>
@@ -5461,13 +5452,13 @@
     </row>
     <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="109" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="D6" s="110">
         <v>700000</v>
@@ -5483,13 +5474,13 @@
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="109" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="D7" s="110">
         <v>700000</v>
@@ -5505,13 +5496,13 @@
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="109" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B8" s="109" t="s">
+        <v>572</v>
+      </c>
+      <c r="C8" s="109" t="s">
         <v>577</v>
-      </c>
-      <c r="C8" s="109" t="s">
-        <v>582</v>
       </c>
       <c r="D8" s="110">
         <v>700000</v>
@@ -5527,13 +5518,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B9" s="109" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D9" s="110">
         <v>700000</v>
@@ -5549,13 +5540,13 @@
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B10" s="109" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C10" s="109" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D10" s="110">
         <v>800000</v>
@@ -5571,7 +5562,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="111" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="B11" s="111"/>
       <c r="C11" s="111"/>
@@ -5598,7 +5589,7 @@
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="111" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="B13" s="109"/>
       <c r="C13" s="109"/>
@@ -5608,28 +5599,28 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B14" s="108" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="C14" s="108"/>
       <c r="D14" s="113" t="s">
         <v>71</v>
       </c>
       <c r="E14" s="113" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="F14" s="113" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="109" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="110">
@@ -5646,10 +5637,10 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="109" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="110">
@@ -5666,10 +5657,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B17" s="109" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="C17" s="109"/>
       <c r="D17" s="110">
@@ -5686,10 +5677,10 @@
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="109" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C18" s="109"/>
       <c r="D18" s="110"/>
@@ -5701,7 +5692,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="111" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B19" s="111"/>
       <c r="C19" s="111"/>
@@ -5722,7 +5713,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="111" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="B21" s="109"/>
       <c r="C21" s="109"/>
@@ -5732,7 +5723,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B22" s="109"/>
       <c r="C22" s="109"/>
@@ -5750,10 +5741,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B23" s="109" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C23" s="109"/>
       <c r="D23" s="110"/>
@@ -5765,10 +5756,10 @@
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="B24" s="109" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C24" s="109"/>
       <c r="D24" s="110"/>
@@ -5780,10 +5771,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C25" s="109"/>
       <c r="D25" s="110"/>
@@ -5951,14 +5942,14 @@
     </row>
     <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="B15" s="8">
         <f>ROUND(0.29%*12*SUMIFS(Штат!$H$5:$H$36,Штат!$E$5:$E$36,"штат",Штат!$F$5:$F$36,"новая"),-3)</f>
         <v>713000</v>
       </c>
       <c r="C15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6149,7 +6140,7 @@
         <v>4869152.0999999996</v>
       </c>
       <c r="C32" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6160,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6187,175 +6178,175 @@
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="41" spans="1:3" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B42" s="13">
         <f>ROUND((52.2+21.4+12.4+33.7+190)*1.1,2)</f>
         <v>340.67</v>
       </c>
       <c r="C42" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B43" s="5">
         <v>13500</v>
       </c>
       <c r="C43" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B44" s="5">
         <f>743*309.7</f>
         <v>230107.1</v>
       </c>
       <c r="C44" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B45" s="5">
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B46" s="5">
         <v>40000</v>
       </c>
       <c r="C46" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B47" s="5">
         <f>Аренда_мес*(1+НДС)</f>
         <v>5648216.4359999988</v>
       </c>
       <c r="C47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B48" s="5">
         <f>Аренда_мес*Депозит_мес</f>
         <v>4869152.0999999996</v>
       </c>
       <c r="C48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B49" s="15">
         <f>11/31+2</f>
         <v>2.3548387096774195</v>
       </c>
       <c r="C49" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B51" s="14">
         <v>0.1</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B52" s="15">
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B55" s="5">
         <v>29613000</v>
       </c>
       <c r="C55" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="B56" s="5">
         <v>7355000</v>
       </c>
       <c r="C56" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="B57" s="5">
         <v>482000</v>
       </c>
       <c r="C57" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -6384,7 +6375,7 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6416,7 +6407,7 @@
         <v>72</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>73</v>
@@ -6425,22 +6416,22 @@
         <v>74</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>76</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -6448,10 +6439,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>78</v>
@@ -6496,7 +6487,7 @@
         <v>3636460</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Q5" s="89"/>
     </row>
@@ -6505,10 +6496,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>81</v>
@@ -6553,7 +6544,7 @@
         <v>3189340</v>
       </c>
       <c r="P6" s="17" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="Q6" s="89"/>
     </row>
@@ -6562,10 +6553,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>81</v>
@@ -6610,7 +6601,7 @@
         <v>3189340</v>
       </c>
       <c r="P7" s="17" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Q7" s="89"/>
     </row>
@@ -6619,10 +6610,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>81</v>
@@ -6667,7 +6658,7 @@
         <v>3223292.3809523811</v>
       </c>
       <c r="P8" s="17" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="Q8" s="89">
         <v>1</v>
@@ -6678,13 +6669,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -6726,7 +6717,7 @@
         <v>1516842.3809523811</v>
       </c>
       <c r="P9" s="17" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Q9" s="89"/>
     </row>
@@ -6735,13 +6726,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>79</v>
@@ -6783,7 +6774,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P10" s="17" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="Q10" s="89">
         <v>1</v>
@@ -6794,16 +6785,16 @@
         <v>6</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>82</v>
@@ -6842,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="21" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="Q11" s="89"/>
     </row>
@@ -6851,13 +6842,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>238</v>
-      </c>
       <c r="D12" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>79</v>
@@ -6899,7 +6890,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P12" s="17" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q12" s="89"/>
     </row>
@@ -6908,13 +6899,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="D13" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>265</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>79</v>
@@ -6956,7 +6947,7 @@
         <v>2552612.3809523811</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Q13" s="89"/>
     </row>
@@ -6965,13 +6956,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>79</v>
@@ -7013,7 +7004,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P14" s="17" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="Q14" s="89">
         <v>1</v>
@@ -7024,13 +7015,13 @@
         <v>17</v>
       </c>
       <c r="B15" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>79</v>
@@ -7072,7 +7063,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P15" s="17" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Q15" s="89">
         <v>1</v>
@@ -7083,13 +7074,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D16" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>79</v>
@@ -7131,7 +7122,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P16" s="17" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="Q16" s="89">
         <v>1</v>
@@ -7142,13 +7133,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>241</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>79</v>
@@ -7190,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -7199,13 +7190,13 @@
         <v>19</v>
       </c>
       <c r="B18" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D18" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>79</v>
@@ -7247,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -7256,13 +7247,13 @@
         <v>19</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>240</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>242</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>79</v>
@@ -7304,7 +7295,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P19" s="17" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="Q19" s="89"/>
     </row>
@@ -7313,13 +7304,13 @@
         <v>23</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -7361,7 +7352,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P20" s="17" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="Q20" s="89">
         <v>1</v>
@@ -7372,16 +7363,16 @@
         <v>24</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F21" s="20" t="s">
         <v>82</v>
@@ -7420,7 +7411,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="21" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q21" s="89"/>
     </row>
@@ -7429,13 +7420,13 @@
         <v>25</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -7477,7 +7468,7 @@
         <v>2999732.3809523811</v>
       </c>
       <c r="P22" s="17" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="Q22" s="89"/>
     </row>
@@ -7486,13 +7477,13 @@
         <v>26</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>248</v>
-      </c>
       <c r="D23" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>79</v>
@@ -7534,7 +7525,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="Q23" s="89">
         <v>1</v>
@@ -7545,16 +7536,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F24" s="20" t="s">
         <v>82</v>
@@ -7593,7 +7584,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q24" s="89"/>
     </row>
@@ -7602,16 +7593,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F25" s="20" t="s">
         <v>82</v>
@@ -7650,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="21" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q25" s="89"/>
     </row>
@@ -7659,13 +7650,13 @@
         <v>29</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>79</v>
@@ -7707,7 +7698,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="Q26" s="89">
         <v>1</v>
@@ -7718,13 +7709,13 @@
         <v>30</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>79</v>
@@ -7766,7 +7757,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P27" s="17" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="Q27" s="89"/>
     </row>
@@ -7775,13 +7766,13 @@
         <v>31</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>79</v>
@@ -7823,7 +7814,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P28" s="17" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Q28" s="89"/>
     </row>
@@ -7832,16 +7823,16 @@
         <v>32</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>82</v>
@@ -7880,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="21" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Q29" s="89"/>
     </row>
@@ -7889,7 +7880,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>83</v>
@@ -7937,7 +7928,7 @@
         <v>3189340</v>
       </c>
       <c r="P30" s="17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q30" s="89"/>
     </row>
@@ -7946,13 +7937,13 @@
         <v>34</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>84</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E31" s="16" t="s">
         <v>79</v>
@@ -7994,7 +7985,7 @@
         <v>1658372.3809523811</v>
       </c>
       <c r="P31" s="17" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Q31" s="89"/>
     </row>
@@ -8003,13 +7994,13 @@
         <v>35</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E32" s="16" t="s">
         <v>79</v>
@@ -8051,7 +8042,7 @@
         <v>2329052.3809523811</v>
       </c>
       <c r="P32" s="17" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="Q32" s="89"/>
     </row>
@@ -8060,13 +8051,13 @@
         <v>35</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E33" s="16" t="s">
         <v>79</v>
@@ -8108,7 +8099,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P33" s="17" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="Q33" s="89"/>
     </row>
@@ -8117,13 +8108,13 @@
         <v>35</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E34" s="16" t="s">
         <v>79</v>
@@ -8165,7 +8156,7 @@
         <v>1881932.3809523811</v>
       </c>
       <c r="P34" s="17" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="Q34" s="89"/>
     </row>
@@ -8174,16 +8165,16 @@
         <v>36</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>82</v>
@@ -8222,7 +8213,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="21" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="Q35" s="89"/>
     </row>
@@ -8231,16 +8222,16 @@
         <v>37</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>270</v>
-      </c>
       <c r="D36" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>82</v>
@@ -8279,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="21" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="Q36" s="89"/>
     </row>
@@ -8287,7 +8278,7 @@
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -8323,7 +8314,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C38" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G38">
         <f>SUM(G8:G12)+SUM(G13:G29)</f>
@@ -8336,7 +8327,7 @@
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C39" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G39">
         <f>G37-G38</f>
@@ -8349,12 +8340,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -8363,7 +8354,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -8372,7 +8363,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -8381,7 +8372,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -8412,7 +8403,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -8420,31 +8411,31 @@
         <v>65</v>
       </c>
       <c r="B3" s="25" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C3" s="25" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="103" t="s">
+        <v>512</v>
+      </c>
+      <c r="G3" s="103" t="s">
+        <v>513</v>
+      </c>
+      <c r="H3" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="I3" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="F3" s="103" t="s">
-        <v>517</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>518</v>
-      </c>
-      <c r="H3" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="I3" s="25" t="s">
-        <v>277</v>
-      </c>
       <c r="J3" s="25" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>75</v>
@@ -8458,13 +8449,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D4" s="27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E4" s="28">
         <v>867500</v>
@@ -8502,13 +8493,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E5" s="28">
         <v>425600</v>
@@ -8546,13 +8537,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>280</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>282</v>
       </c>
       <c r="E6" s="28">
         <v>1000000</v>
@@ -8590,13 +8581,13 @@
         <v>4</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>283</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>285</v>
       </c>
       <c r="E7" s="28">
         <v>1000000</v>
@@ -8634,13 +8625,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E8" s="28">
         <v>700000</v>
@@ -8678,13 +8669,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E9" s="28">
         <v>700000</v>
@@ -8722,13 +8713,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E10" s="28">
         <v>700000</v>
@@ -8764,7 +8755,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -8797,7 +8788,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -8819,12 +8810,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8835,48 +8826,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
+        <v>494</v>
+      </c>
+      <c r="B7" s="95" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="95" t="s">
+        <v>496</v>
+      </c>
+      <c r="D7" s="95" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="95" t="s">
+        <v>498</v>
+      </c>
+      <c r="F7" s="95" t="s">
         <v>499</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>500</v>
-      </c>
-      <c r="C7" s="95" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" s="95" t="s">
-        <v>502</v>
-      </c>
-      <c r="E7" s="95" t="s">
-        <v>503</v>
-      </c>
-      <c r="F7" s="95" t="s">
-        <v>504</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8997,48 +8988,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -9048,7 +9039,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -9058,7 +9049,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -9068,7 +9059,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -9078,7 +9069,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -9088,7 +9079,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
@@ -9112,12 +9103,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9137,7 +9128,7 @@
         <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>90</v>
@@ -9217,7 +9208,7 @@
     </row>
     <row r="8" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C8">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент социологических*",Штат!$E$5:$E$36,"штат")</f>
@@ -9240,7 +9231,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -9263,7 +9254,7 @@
     </row>
     <row r="10" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C10">
         <f>SUM(Штат!G20:G21)</f>
@@ -9286,7 +9277,7 @@
     </row>
     <row r="11" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C11">
         <f>SUM(Штат!G22:G29)</f>
@@ -9347,12 +9338,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>616</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9375,7 +9366,7 @@
         <v>95</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>96</v>
@@ -9384,16 +9375,16 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9419,7 +9410,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I57" si="0">IF(F5="разово",IF(G5&lt;=3,D5*E5,0),IF(F5="мес",D5*E5*MAX(0,4-G5),D5*E5*MAX(0,4-G5)/12))</f>
@@ -9464,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
@@ -9509,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -9536,7 +9527,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -9555,7 +9546,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -9582,7 +9573,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -9601,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9" si="4">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
@@ -9628,7 +9619,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -9647,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10" si="5">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
@@ -9674,7 +9665,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -9693,7 +9684,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11" si="6">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
@@ -9720,7 +9711,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -9739,7 +9730,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -9766,7 +9757,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -9785,7 +9776,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
@@ -9812,7 +9803,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -9831,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
@@ -9858,7 +9849,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9877,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" ref="I15" si="7">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
@@ -9904,7 +9895,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9923,7 +9914,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" ref="I16:I21" si="8">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
@@ -9950,7 +9941,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9969,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="8"/>
@@ -9996,7 +9987,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -10015,7 +10006,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="8"/>
@@ -10042,7 +10033,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -10061,7 +10052,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="8"/>
@@ -10088,7 +10079,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -10107,7 +10098,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="8"/>
@@ -10134,7 +10125,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -10153,7 +10144,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="8"/>
@@ -10223,7 +10214,7 @@
         <v>97</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C23" t="s">
         <v>103</v>
@@ -10266,7 +10257,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -10284,7 +10275,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -10311,7 +10302,7 @@
         <v>97</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
         <v>99</v>
@@ -10329,7 +10320,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="0"/>
@@ -10356,7 +10347,7 @@
         <v>97</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C26" t="s">
         <v>103</v>
@@ -10375,7 +10366,7 @@
         <v>1</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="0"/>
@@ -10402,7 +10393,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -10421,7 +10412,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
@@ -10448,7 +10439,7 @@
         <v>97</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
@@ -10466,7 +10457,7 @@
         <v>1</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="0"/>
@@ -10493,7 +10484,7 @@
         <v>97</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
         <v>103</v>
@@ -10536,7 +10527,7 @@
         <v>97</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C30" t="s">
         <v>99</v>
@@ -10554,7 +10545,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="0"/>
@@ -10581,7 +10572,7 @@
         <v>97</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
         <v>99</v>
@@ -10599,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="0"/>
@@ -10626,7 +10617,7 @@
         <v>97</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
         <v>103</v>
@@ -10644,7 +10635,7 @@
         <v>1</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I32" s="5">
         <f t="shared" si="0"/>
@@ -10671,7 +10662,7 @@
         <v>97</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C33" t="s">
         <v>99</v>
@@ -10688,7 +10679,7 @@
         <v>1</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I33" s="5">
         <f t="shared" si="0"/>
@@ -10715,10 +10706,10 @@
         <v>97</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C34" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D34" s="9"/>
       <c r="E34" s="10">
@@ -10732,7 +10723,7 @@
         <v>1</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="0"/>
@@ -10759,7 +10750,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C35" t="s">
         <v>99</v>
@@ -10776,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="0"/>
@@ -10803,7 +10794,7 @@
         <v>97</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
         <v>103</v>
@@ -10820,7 +10811,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="0"/>
@@ -10847,7 +10838,7 @@
         <v>97</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C37" t="s">
         <v>99</v>
@@ -10866,7 +10857,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="0"/>
@@ -10893,7 +10884,7 @@
         <v>97</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C38" t="s">
         <v>99</v>
@@ -10912,7 +10903,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="0"/>
@@ -10939,7 +10930,7 @@
         <v>97</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C39" t="s">
         <v>99</v>
@@ -10958,7 +10949,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="0"/>
@@ -10985,7 +10976,7 @@
         <v>97</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C40" t="s">
         <v>99</v>
@@ -11004,7 +10995,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="0"/>
@@ -11031,7 +11022,7 @@
         <v>97</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C41" t="s">
         <v>99</v>
@@ -11050,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I41" s="5">
         <f t="shared" ref="I41" si="12">IF(F41="разово",IF(G41&lt;=3,D41*E41,0),IF(F41="мес",D41*E41*MAX(0,4-G41),D41*E41*MAX(0,4-G41)/12))</f>
@@ -11077,7 +11068,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -11096,7 +11087,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
@@ -11123,7 +11114,7 @@
         <v>97</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C43" t="s">
         <v>99</v>
@@ -11142,7 +11133,7 @@
         <v>1</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="0"/>
@@ -11169,7 +11160,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -11188,7 +11179,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
@@ -11215,7 +11206,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -11234,7 +11225,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
@@ -11261,7 +11252,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -11279,7 +11270,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
@@ -11394,7 +11385,7 @@
         <v>97</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s">
         <v>108</v>
@@ -11413,7 +11404,7 @@
         <v>1</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="0"/>
@@ -11440,7 +11431,7 @@
         <v>97</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C50" t="s">
         <v>103</v>
@@ -11483,7 +11474,7 @@
         <v>97</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C51" t="s">
         <v>99</v>
@@ -11502,7 +11493,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" ref="I51" si="13">IF(F51="разово",IF(G51&lt;=3,D51*E51,0),IF(F51="мес",D51*E51*MAX(0,4-G51),D51*E51*MAX(0,4-G51)/12))</f>
@@ -11529,7 +11520,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -11548,7 +11539,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" ref="I52:I54" si="14">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
@@ -11575,7 +11566,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -11594,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="14"/>
@@ -11621,7 +11612,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C54" t="s">
         <v>99</v>
@@ -11640,7 +11631,7 @@
         <v>1</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="14"/>
@@ -11753,7 +11744,7 @@
         <v>97</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C57" t="s">
         <v>99</v>
@@ -11815,7 +11806,7 @@
         <v>1</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I58" s="5">
         <f>D58*E58*Аренда_мес_2026</f>
@@ -11840,7 +11831,7 @@
         <v>111</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C59" t="s">
         <v>115</v>
@@ -11859,7 +11850,7 @@
         <v>1</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" ref="I59:I77" si="15">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
@@ -11904,7 +11895,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="15"/>
@@ -12011,10 +12002,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="C63" s="105" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -12030,7 +12021,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
@@ -12096,7 +12087,7 @@
         <v>111</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C65" t="s">
         <v>113</v>
@@ -12115,7 +12106,7 @@
         <v>2</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="15"/>
@@ -12140,7 +12131,7 @@
         <v>111</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -12159,7 +12150,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="I66" s="5">
         <f t="shared" ref="I66" si="17">IF(F66="разово",IF(G66&lt;=3,D66*E66,0),IF(F66="мес",D66*E66*MAX(0,4-G66),D66*E66*MAX(0,4-G66)/12))</f>
@@ -12245,7 +12236,7 @@
         <v>2</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" si="15"/>
@@ -12354,7 +12345,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -12373,7 +12364,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="15"/>
@@ -12400,10 +12391,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C72" s="102" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -12418,7 +12409,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
@@ -12443,15 +12434,15 @@
         <v>128</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C73" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="10"/>
       <c r="F73" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G73" s="9"/>
       <c r="H73" s="4"/>
@@ -12518,7 +12509,7 @@
         <v>128</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C75" t="s">
         <v>113</v>
@@ -12556,10 +12547,10 @@
     </row>
     <row r="76" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -12577,7 +12568,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="15"/>
@@ -12600,42 +12591,16 @@
       </c>
     </row>
     <row r="77" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>132</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C77" t="s">
-        <v>130</v>
-      </c>
+      <c r="B77" s="4"/>
       <c r="D77" s="9"/>
-      <c r="E77" s="10">
-        <v>100000</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="G77" s="9">
-        <v>2</v>
-      </c>
+      <c r="E77" s="10"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
       <c r="H77" s="4"/>
-      <c r="I77" s="5">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="J77" s="5">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="K77" s="5">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="L77" s="5">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
       <c r="M77" s="89"/>
     </row>
   </sheetData>
@@ -12664,7 +12629,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -12693,29 +12658,29 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="I4" s="34" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="J4" s="34" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
       <c r="F5" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G5" s="5">
         <f>'Taza talqy'!F12</f>
@@ -12736,18 +12701,18 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
       <c r="F6" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G6" s="5">
         <f>'Презентация офисе'!F15</f>
@@ -12768,18 +12733,18 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
       <c r="F7" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G7" s="5">
         <f>'креативные проекты'!F9</f>
@@ -12800,18 +12765,18 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
       <c r="F8" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G8" s="5">
         <f>'Информ сопровождение'!F13</f>
@@ -12832,18 +12797,18 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
       <c r="F9" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G9" s="5">
         <f>'Соц исследования'!F8</f>
@@ -12864,18 +12829,18 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
       <c r="F10" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G10" s="5">
         <f>'Разработка платформы'!F7</f>
@@ -12912,7 +12877,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -12959,7 +12924,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="28.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="114" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B1" s="114"/>
       <c r="C1" s="114"/>
@@ -12978,25 +12943,25 @@
         <v>65</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="48" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C4" s="49"/>
       <c r="D4" s="49"/>
@@ -13008,13 +12973,13 @@
     </row>
     <row r="5" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D5" s="55">
         <v>56</v>
@@ -13029,13 +12994,13 @@
     </row>
     <row r="6" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="B6" s="57" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C6" s="55" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D6" s="55">
         <v>56</v>
@@ -13051,13 +13016,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B7" s="57" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C7" s="55" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D7" s="55">
         <v>6</v>
@@ -13072,13 +13037,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="51" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="B8" s="57" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D8" s="55">
         <v>6</v>
@@ -13093,13 +13058,13 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="51" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B9" s="57" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C9" s="55" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D9" s="55">
         <v>6</v>
@@ -13114,13 +13079,13 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="51" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C10" s="55" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D10" s="55">
         <v>48</v>
@@ -13136,7 +13101,7 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="51"/>
       <c r="B11" s="59" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="C11" s="49"/>
       <c r="D11" s="55"/>
@@ -13149,7 +13114,7 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="51"/>
       <c r="B12" s="60" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -2094,9 +2094,6 @@
     <t>Финансирование</t>
   </si>
   <si>
-    <t>Разница с 250 млн (+ остаток / − не хватает)</t>
-  </si>
-  <si>
     <t>В. Долг по зарплате и налогам за июль–октябрь 2026</t>
   </si>
   <si>
@@ -2266,6 +2263,9 @@
   </si>
   <si>
     <t>Резерв 10% и прочие расходы (прочая кредиторская задолженность)</t>
+  </si>
+  <si>
+    <t>Разница с 250 млн (+ остаток / − дефицит)</t>
   </si>
 </sst>
 </file>
@@ -3011,7 +3011,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3028,10 +3028,10 @@
         <v>557</v>
       </c>
       <c r="E3" s="35" t="s">
+        <v>605</v>
+      </c>
+      <c r="F3" s="35" t="s">
         <v>606</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Долг_ЗП</f>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B16" s="38">
         <f>(B15-Долг_ЗП-'Оснащение и офис'!$J$76)*Резерв+Долг_прочие</f>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B17" s="38">
         <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС</f>
@@ -3416,7 +3416,7 @@
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B20" s="40">
         <f>Долг_ЗП+Долг_НДС+Долг_прочие</f>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>561</v>
+        <v>618</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -5383,7 +5383,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5391,30 +5391,30 @@
         <v>67</v>
       </c>
       <c r="B3" s="108" t="s">
+        <v>565</v>
+      </c>
+      <c r="C3" s="108" t="s">
         <v>566</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="D3" s="108" t="s">
         <v>567</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="E3" s="108" t="s">
         <v>568</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="F3" s="108" t="s">
         <v>569</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
+        <v>570</v>
+      </c>
+      <c r="B4" s="109" t="s">
         <v>571</v>
       </c>
-      <c r="B4" s="109" t="s">
+      <c r="C4" s="109" t="s">
         <v>572</v>
-      </c>
-      <c r="C4" s="109" t="s">
-        <v>573</v>
       </c>
       <c r="D4" s="110">
         <v>1300000</v>
@@ -5433,10 +5433,10 @@
         <v>239</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D5" s="110">
         <v>1000000</v>
@@ -5455,10 +5455,10 @@
         <v>241</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D6" s="110">
         <v>700000</v>
@@ -5477,10 +5477,10 @@
         <v>241</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D7" s="110">
         <v>700000</v>
@@ -5499,10 +5499,10 @@
         <v>241</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D8" s="110">
         <v>700000</v>
@@ -5518,13 +5518,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
+        <v>577</v>
+      </c>
+      <c r="B9" s="109" t="s">
         <v>578</v>
       </c>
-      <c r="B9" s="109" t="s">
+      <c r="C9" s="109" t="s">
         <v>579</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>580</v>
       </c>
       <c r="D9" s="110">
         <v>700000</v>
@@ -5540,13 +5540,13 @@
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
+        <v>580</v>
+      </c>
+      <c r="B10" s="109" t="s">
         <v>581</v>
       </c>
-      <c r="B10" s="109" t="s">
+      <c r="C10" s="109" t="s">
         <v>582</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>583</v>
       </c>
       <c r="D10" s="110">
         <v>800000</v>
@@ -5562,7 +5562,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B11" s="111"/>
       <c r="C11" s="111"/>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="111" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B13" s="109"/>
       <c r="C13" s="109"/>
@@ -5602,25 +5602,25 @@
         <v>173</v>
       </c>
       <c r="B14" s="108" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C14" s="108"/>
       <c r="D14" s="113" t="s">
         <v>71</v>
       </c>
       <c r="E14" s="113" t="s">
+        <v>586</v>
+      </c>
+      <c r="F14" s="113" t="s">
         <v>587</v>
-      </c>
-      <c r="F14" s="113" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="109" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="109" t="s">
         <v>589</v>
-      </c>
-      <c r="B15" s="109" t="s">
-        <v>590</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="110">
@@ -5637,10 +5637,10 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="109" t="s">
+        <v>590</v>
+      </c>
+      <c r="B16" s="109" t="s">
         <v>591</v>
-      </c>
-      <c r="B16" s="109" t="s">
-        <v>592</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="110">
@@ -5657,10 +5657,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
+        <v>592</v>
+      </c>
+      <c r="B17" s="109" t="s">
         <v>593</v>
-      </c>
-      <c r="B17" s="109" t="s">
-        <v>594</v>
       </c>
       <c r="C17" s="109"/>
       <c r="D17" s="110">
@@ -5680,7 +5680,7 @@
         <v>212</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C18" s="109"/>
       <c r="D18" s="110"/>
@@ -5692,7 +5692,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="111" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B19" s="111"/>
       <c r="C19" s="111"/>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="111" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B21" s="109"/>
       <c r="C21" s="109"/>
@@ -5723,7 +5723,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B22" s="109"/>
       <c r="C22" s="109"/>
@@ -5741,10 +5741,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
+        <v>598</v>
+      </c>
+      <c r="B23" s="109" t="s">
         <v>599</v>
-      </c>
-      <c r="B23" s="109" t="s">
-        <v>600</v>
       </c>
       <c r="C23" s="109"/>
       <c r="D23" s="110"/>
@@ -5756,10 +5756,10 @@
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
+        <v>600</v>
+      </c>
+      <c r="B24" s="109" t="s">
         <v>601</v>
-      </c>
-      <c r="B24" s="109" t="s">
-        <v>602</v>
       </c>
       <c r="C24" s="109"/>
       <c r="D24" s="110"/>
@@ -5771,10 +5771,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
+        <v>602</v>
+      </c>
+      <c r="B25" s="109" t="s">
         <v>603</v>
-      </c>
-      <c r="B25" s="109" t="s">
-        <v>604</v>
       </c>
       <c r="C25" s="109"/>
       <c r="D25" s="110"/>
@@ -6313,40 +6313,40 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B55" s="5">
         <v>29613000</v>
       </c>
       <c r="C55" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B56" s="5">
         <v>7355000</v>
       </c>
       <c r="C56" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B57" s="5">
         <v>482000</v>
       </c>
       <c r="C57" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -9338,7 +9338,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11853,11 +11853,11 @@
         <v>254</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" ref="I59:I77" si="15">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
+        <f t="shared" ref="I59:I76" si="15">IF(F59="разово",IF(G59&lt;=3,D59*E59,0),IF(F59="мес",D59*E59*MAX(0,4-G59),D59*E59*MAX(0,4-G59)/12))</f>
         <v>4869152.0999999996</v>
       </c>
       <c r="J59" s="5">
-        <f t="shared" ref="J59:J77" si="16">IF($F59="разово",IF($M59=12,0,$I59),IF($F59="мес",$D59*$E59*(($G59&lt;=1)+($G59&lt;=2)),IF($F59="год",$D59*$E59/12*(($G59&lt;=1)+($G59&lt;=2)),$I59/2)))</f>
+        <f t="shared" ref="J59:J76" si="16">IF($F59="разово",IF($M59=12,0,$I59),IF($F59="мес",$D59*$E59*(($G59&lt;=1)+($G59&lt;=2)),IF($F59="год",$D59*$E59/12*(($G59&lt;=1)+($G59&lt;=2)),$I59/2)))</f>
         <v>4869152.0999999996</v>
       </c>
       <c r="K59" s="5">
@@ -12288,11 +12288,11 @@
         <v>22500</v>
       </c>
       <c r="K69" s="5">
-        <f t="shared" ref="K69:K77" si="18">IF($F69="разово",IF($M69=12,$I69,0),IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
+        <f t="shared" ref="K69:K76" si="18">IF($F69="разово",IF($M69=12,$I69,0),IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
         <v>22500</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" ref="L69:L77" si="19">IF($F69="разово",0,IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
+        <f t="shared" ref="L69:L76" si="19">IF($F69="разово",0,IF($F69="мес",$D69*$E69*($G69&lt;=3),IF($F69="год",$D69*$E69/12*($G69&lt;=3),$I69/2)))</f>
         <v>22500</v>
       </c>
       <c r="M69" s="89"/>

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -2253,9 +2253,6 @@
     <t>Прочая кредиторская задолженность – в строке «Резерв и прочие расходы»</t>
   </si>
   <si>
-    <t>НДС: 16% на закупки, аренду, услуги и подписки; расчёты с бюджетом по НДС</t>
-  </si>
-  <si>
     <t>Оснащение, офис, цифровые инструменты и медиа на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
@@ -2266,6 +2263,9 @@
   </si>
   <si>
     <t>Разница с 250 млн (+ остаток / − дефицит)</t>
+  </si>
+  <si>
+    <t>НДС: 16% на закупки, аренду, услуги, подписки и первоочередные проекты; расчёты с бюджетом по НДС</t>
   </si>
 </sst>
 </file>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3316,7 +3316,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B16" s="38">
         <f>(B15-Долг_ЗП-'Оснащение и офис'!$J$76)*Резерв+Долг_прочие</f>
@@ -3339,29 +3339,29 @@
         <v>21679569.428648233</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B17" s="38">
-        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС</f>
-        <v>11016668.674116129</v>
+        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС+B19*НДС</f>
+        <v>17136024.407449462</v>
       </c>
       <c r="C17" s="38">
-        <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59-'Оснащение и офис'!$K$76)*(1+Резерв)*НДС</f>
-        <v>1467285.9696000002</v>
+        <f>((C11+C12+C13+C14)-'Оснащение и офис'!$K$59-'Оснащение и офис'!$K$76)*(1+Резерв)*НДС+C19*НДС</f>
+        <v>6560273.7029333338</v>
       </c>
       <c r="D17" s="38">
-        <f>((D11+D12+D13+D14)-'Оснащение и офис'!$L$59-'Оснащение и офис'!$L$76)*(1+Резерв)*НДС</f>
-        <v>1168858.7856000001</v>
+        <f>((D11+D12+D13+D14)-'Оснащение и офис'!$L$59-'Оснащение и офис'!$L$76)*(1+Резерв)*НДС+D19*НДС</f>
+        <v>3914006.5189333335</v>
       </c>
       <c r="E17" s="38">
-        <f>(E11+E12+E13+E14)*(1+Резерв)*НДС</f>
-        <v>1266467.3296000001</v>
+        <f>(E11+E12+E13+E14)*(1+Резерв)*НДС+E19*НДС</f>
+        <v>5918964.3962666672</v>
       </c>
       <c r="F17" s="38">
         <f t="shared" si="0"/>
-        <v>14919280.75891613</v>
+        <v>33529269.025582798</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -3370,23 +3370,23 @@
       </c>
       <c r="B18" s="42">
         <f>B15+B16+B17</f>
-        <v>109441146.4342467</v>
+        <v>115560502.16758004</v>
       </c>
       <c r="C18" s="42">
         <f>C15+C16+C17</f>
-        <v>61625850.754600003</v>
+        <v>66718838.487933338</v>
       </c>
       <c r="D18" s="42">
         <f>D15+D16+D17</f>
-        <v>49199059.795600004</v>
+        <v>51944207.528933339</v>
       </c>
       <c r="E18" s="42">
         <f>E15+E16+E17</f>
-        <v>58271487.489600003</v>
+        <v>62923984.556266673</v>
       </c>
       <c r="F18" s="42">
         <f t="shared" si="0"/>
-        <v>278537544.47404671</v>
+        <v>297147532.74071342</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3442,23 +3442,23 @@
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
-        <v>147687119.76758003</v>
+        <v>153806475.50091338</v>
       </c>
       <c r="C21" s="44">
         <f>C18+C19</f>
-        <v>93457024.087933332</v>
+        <v>98550011.821266666</v>
       </c>
       <c r="D21" s="44">
         <f>D18+D19</f>
-        <v>66356233.12893334</v>
+        <v>69101380.862266675</v>
       </c>
       <c r="E21" s="44">
         <f>E18+E19</f>
-        <v>87349594.156266674</v>
+        <v>92002091.222933337</v>
       </c>
       <c r="F21" s="44">
         <f>F18+F19</f>
-        <v>394849971.14071339</v>
+        <v>413459959.4073801</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3467,19 +3467,19 @@
       </c>
       <c r="B23" s="44">
         <f>B21</f>
-        <v>147687119.76758003</v>
+        <v>153806475.50091338</v>
       </c>
       <c r="C23" s="44">
         <f>B23+C21</f>
-        <v>241144143.85551336</v>
+        <v>252356487.32218003</v>
       </c>
       <c r="D23" s="44">
         <f>C23+D21</f>
-        <v>307500376.9844467</v>
+        <v>321457868.18444669</v>
       </c>
       <c r="E23" s="44">
         <f>D23+E21</f>
-        <v>394849971.14071339</v>
+        <v>413459959.40738004</v>
       </c>
       <c r="F23" s="44"/>
     </row>
@@ -3497,27 +3497,27 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
-        <v>102312880.23241997</v>
+        <v>96193524.499086618</v>
       </c>
       <c r="C25" s="44">
         <f>$F$24-C23</f>
-        <v>8855856.1444866359</v>
+        <v>-2356487.3221800327</v>
       </c>
       <c r="D25" s="44">
         <f>$F$24-D23</f>
-        <v>-57500376.984446704</v>
+        <v>-71457868.184446692</v>
       </c>
       <c r="E25" s="44">
         <f>$F$24-E23</f>
-        <v>-144849971.14071339</v>
+        <v>-163459959.40738004</v>
       </c>
       <c r="F25" s="44">
         <f>F24-F21</f>
-        <v>-144849971.14071339</v>
+        <v>-163459959.4073801</v>
       </c>
     </row>
   </sheetData>
@@ -9338,7 +9338,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -2250,22 +2250,22 @@
     <t>Долг_прочие</t>
   </si>
   <si>
-    <t>Прочая кредиторская задолженность – в строке «Резерв и прочие расходы»</t>
-  </si>
-  <si>
     <t>Оснащение, офис, цифровые инструменты и медиа на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
-    <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские, нотариус и услуги МФЦА</t>
-  </si>
-  <si>
-    <t>Резерв 10% и прочие расходы (прочая кредиторская задолженность)</t>
-  </si>
-  <si>
     <t>Разница с 250 млн (+ остаток / − дефицит)</t>
   </si>
   <si>
     <t>НДС: 16% на закупки, аренду, услуги, подписки и первоочередные проекты; расчёты с бюджетом по НДС</t>
+  </si>
+  <si>
+    <t>6. Офис: аренда, депозит, текущие хозрасходы, курьер, интернет, обслуживание МФУ, канцелярия, представительские, нотариус и услуги МФЦА, расчёты с поставщиками за прошлые периоды</t>
+  </si>
+  <si>
+    <t>Резерв 10% на непредвиденные расходы</t>
+  </si>
+  <si>
+    <t>Прочая кредиторская задолженность – в строке «Офис» (без резерва и НДС)</t>
   </si>
 </sst>
 </file>
@@ -3214,13 +3214,13 @@
         <v>14537636.9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B12" s="38">
-        <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
-        <v>12179706.848387096</v>
+        <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")+Долг_прочие</f>
+        <v>12661706.848387096</v>
       </c>
       <c r="C12" s="38">
         <f>SUMIFS('Оснащение и офис'!$K$5:$K$77,'Оснащение и офис'!$A$5:$A$77,"Офис")</f>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F12" s="38">
         <f t="shared" si="0"/>
-        <v>27817936.148387097</v>
+        <v>28299936.148387097</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="B15" s="40">
         <f>SUM(B6:B14)-B7</f>
-        <v>91762525.236482337</v>
+        <v>92244525.236482337</v>
       </c>
       <c r="C15" s="40">
         <f>SUM(C6:C14)-C7</f>
@@ -3311,16 +3311,16 @@
       </c>
       <c r="F15" s="40">
         <f t="shared" si="0"/>
-        <v>241938694.28648233</v>
+        <v>242420694.28648233</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B16" s="38">
-        <f>(B15-Долг_ЗП-'Оснащение и офис'!$J$76)*Резерв+Долг_прочие</f>
-        <v>6661952.5236482341</v>
+        <f>(B15-Долг_ЗП-Долг_прочие-'Оснащение и офис'!$J$76)*Резерв</f>
+        <v>6179952.5236482341</v>
       </c>
       <c r="C16" s="38">
         <f>(C15-C20-'Оснащение и офис'!$K$76)*Резерв</f>
@@ -3336,15 +3336,15 @@
       </c>
       <c r="F16" s="38">
         <f t="shared" si="0"/>
-        <v>21679569.428648233</v>
+        <v>21197569.428648233</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B17" s="38">
-        <f>((B11+B12+B13+B14)-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС+B19*НДС</f>
+        <f>((B11+B12+B13+B14)-Долг_прочие-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС+B19*НДС</f>
         <v>17136024.407449462</v>
       </c>
       <c r="C17" s="38">
@@ -3497,7 +3497,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -6346,7 +6346,7 @@
         <v>482000</v>
       </c>
       <c r="C57" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -9338,7 +9338,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -94,9 +94,9 @@
     <definedName name="Дней_РК" localSheetId="13">#REF!</definedName>
     <definedName name="Дней_РК" localSheetId="12">#REF!</definedName>
     <definedName name="Дней_РК">Параметры!$B$21</definedName>
-    <definedName name="Долг_ЗП">Параметры!$B$55</definedName>
-    <definedName name="Долг_НДС">Параметры!$B$56</definedName>
-    <definedName name="Долг_прочие">Параметры!$B$57</definedName>
+    <definedName name="Долг_ЗП" hidden="1">Параметры!$B$55</definedName>
+    <definedName name="Долг_НДС" hidden="1">Параметры!$B$56</definedName>
+    <definedName name="Долг_прочие" hidden="1">Параметры!$B$57</definedName>
     <definedName name="Кап_ООСМС" localSheetId="8">#REF!</definedName>
     <definedName name="Кап_ООСМС" localSheetId="11">#REF!</definedName>
     <definedName name="Кап_ООСМС" localSheetId="10">#REF!</definedName>
@@ -167,6 +167,9 @@
     <definedName name="Ночей_РК" localSheetId="13">#REF!</definedName>
     <definedName name="Ночей_РК" localSheetId="12">#REF!</definedName>
     <definedName name="Ночей_РК">Параметры!$B$22</definedName>
+    <definedName name="Обязательства_ЗП">Параметры!$B$55</definedName>
+    <definedName name="Обязательства_НДС">Параметры!$B$56</definedName>
+    <definedName name="Обязательства_прочие">Параметры!$B$57</definedName>
     <definedName name="ОСНС" localSheetId="8">#REF!</definedName>
     <definedName name="ОСНС" localSheetId="11">#REF!</definedName>
     <definedName name="ОСНС" localSheetId="10">#REF!</definedName>
@@ -385,7 +388,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="620">
   <si>
     <t>Статья</t>
   </si>
@@ -2094,9 +2097,6 @@
     <t>Финансирование</t>
   </si>
   <si>
-    <t>В. Долг по зарплате и налогам за июль–октябрь 2026</t>
-  </si>
-  <si>
     <t>1. Оплата труда и отчисления работодателя</t>
   </si>
   <si>
@@ -2232,24 +2232,9 @@
     <t>Итого ноябрь 2026 – февраль 2027</t>
   </si>
   <si>
-    <t>Задолженность Фонда на 01.11.2026 (погашение в ноябре)</t>
-  </si>
-  <si>
-    <t>Долг_ЗП</t>
-  </si>
-  <si>
     <t>Оплата труда за июль–октябрь 2026 с налогами – в строке «Оплата труда»</t>
   </si>
   <si>
-    <t>Долг_НДС</t>
-  </si>
-  <si>
-    <t>Задолженность по НДС – в строке НДС</t>
-  </si>
-  <si>
-    <t>Долг_прочие</t>
-  </si>
-  <si>
     <t>Оснащение, офис, цифровые инструменты и медиа на октябрь–декабрь 2026 года, ₸</t>
   </si>
   <si>
@@ -2265,7 +2250,28 @@
     <t>Резерв 10% на непредвиденные расходы</t>
   </si>
   <si>
-    <t>Прочая кредиторская задолженность – в строке «Офис» (без резерва и НДС)</t>
+    <t>В. Обязательства по оплате труда и налогам за июль–октябрь 2026</t>
+  </si>
+  <si>
+    <t>Обязательства_ЗП</t>
+  </si>
+  <si>
+    <t>Обязательства_НДС</t>
+  </si>
+  <si>
+    <t>Обязательства_прочие</t>
+  </si>
+  <si>
+    <t>Обязательства Фонда на 01.11.2026 (погашение в ноябре)</t>
+  </si>
+  <si>
+    <t>Обязательства по НДС – в строке НДС</t>
+  </si>
+  <si>
+    <t>Прочие обязательства – в строке «Офис» (без резерва и НДС)</t>
+  </si>
+  <si>
+    <t>Октябрь-ноябрь 2026</t>
   </si>
 </sst>
 </file>
@@ -3011,7 +3017,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3019,7 +3025,7 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>555</v>
+        <v>619</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>556</v>
@@ -3028,10 +3034,10 @@
         <v>557</v>
       </c>
       <c r="E3" s="35" t="s">
+        <v>604</v>
+      </c>
+      <c r="F3" s="35" t="s">
         <v>605</v>
-      </c>
-      <c r="F3" s="35" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3071,10 +3077,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B6" s="38">
-        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Долг_ЗП</f>
+        <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Обязательства_ЗП</f>
         <v>56312240</v>
       </c>
       <c r="C6" s="38">
@@ -3216,10 +3222,10 @@
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="B12" s="38">
-        <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")+Долг_прочие</f>
+        <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")+Обязательства_прочие</f>
         <v>12661706.848387096</v>
       </c>
       <c r="C12" s="38">
@@ -3316,10 +3322,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="B16" s="38">
-        <f>(B15-Долг_ЗП-Долг_прочие-'Оснащение и офис'!$J$76)*Резерв</f>
+        <f>(B15-Обязательства_ЗП-Обязательства_прочие-'Оснащение и офис'!$J$76)*Резерв</f>
         <v>6179952.5236482341</v>
       </c>
       <c r="C16" s="38">
@@ -3341,10 +3347,10 @@
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="B17" s="38">
-        <f>((B11+B12+B13+B14)-Долг_прочие-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Долг_НДС+B19*НДС</f>
+        <f>((B11+B12+B13+B14)-Обязательства_прочие-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Обязательства_НДС+B19*НДС</f>
         <v>17136024.407449462</v>
       </c>
       <c r="C17" s="38">
@@ -3416,10 +3422,10 @@
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>561</v>
+        <v>612</v>
       </c>
       <c r="B20" s="40">
-        <f>Долг_ЗП+Долг_НДС+Долг_прочие</f>
+        <f>Обязательства_ЗП+Обязательства_НДС+Обязательства_прочие</f>
         <v>37450000</v>
       </c>
       <c r="C20" s="40">
@@ -3438,7 +3444,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3497,7 +3503,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -5383,7 +5389,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5391,30 +5397,30 @@
         <v>67</v>
       </c>
       <c r="B3" s="108" t="s">
+        <v>564</v>
+      </c>
+      <c r="C3" s="108" t="s">
         <v>565</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="D3" s="108" t="s">
         <v>566</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="E3" s="108" t="s">
         <v>567</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="F3" s="108" t="s">
         <v>568</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
+        <v>569</v>
+      </c>
+      <c r="B4" s="109" t="s">
         <v>570</v>
       </c>
-      <c r="B4" s="109" t="s">
+      <c r="C4" s="109" t="s">
         <v>571</v>
-      </c>
-      <c r="C4" s="109" t="s">
-        <v>572</v>
       </c>
       <c r="D4" s="110">
         <v>1300000</v>
@@ -5433,10 +5439,10 @@
         <v>239</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D5" s="110">
         <v>1000000</v>
@@ -5455,10 +5461,10 @@
         <v>241</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D6" s="110">
         <v>700000</v>
@@ -5477,10 +5483,10 @@
         <v>241</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D7" s="110">
         <v>700000</v>
@@ -5499,10 +5505,10 @@
         <v>241</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D8" s="110">
         <v>700000</v>
@@ -5518,13 +5524,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
+        <v>576</v>
+      </c>
+      <c r="B9" s="109" t="s">
         <v>577</v>
       </c>
-      <c r="B9" s="109" t="s">
+      <c r="C9" s="109" t="s">
         <v>578</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>579</v>
       </c>
       <c r="D9" s="110">
         <v>700000</v>
@@ -5540,13 +5546,13 @@
     </row>
     <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
+        <v>579</v>
+      </c>
+      <c r="B10" s="109" t="s">
         <v>580</v>
       </c>
-      <c r="B10" s="109" t="s">
+      <c r="C10" s="109" t="s">
         <v>581</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>582</v>
       </c>
       <c r="D10" s="110">
         <v>800000</v>
@@ -5562,7 +5568,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="111" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B11" s="111"/>
       <c r="C11" s="111"/>
@@ -5589,7 +5595,7 @@
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="111" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B13" s="109"/>
       <c r="C13" s="109"/>
@@ -5602,25 +5608,25 @@
         <v>173</v>
       </c>
       <c r="B14" s="108" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C14" s="108"/>
       <c r="D14" s="113" t="s">
         <v>71</v>
       </c>
       <c r="E14" s="113" t="s">
+        <v>585</v>
+      </c>
+      <c r="F14" s="113" t="s">
         <v>586</v>
-      </c>
-      <c r="F14" s="113" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="109" t="s">
+        <v>587</v>
+      </c>
+      <c r="B15" s="109" t="s">
         <v>588</v>
-      </c>
-      <c r="B15" s="109" t="s">
-        <v>589</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="110">
@@ -5637,10 +5643,10 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="109" t="s">
+        <v>589</v>
+      </c>
+      <c r="B16" s="109" t="s">
         <v>590</v>
-      </c>
-      <c r="B16" s="109" t="s">
-        <v>591</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="110">
@@ -5657,10 +5663,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
+        <v>591</v>
+      </c>
+      <c r="B17" s="109" t="s">
         <v>592</v>
-      </c>
-      <c r="B17" s="109" t="s">
-        <v>593</v>
       </c>
       <c r="C17" s="109"/>
       <c r="D17" s="110">
@@ -5680,7 +5686,7 @@
         <v>212</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C18" s="109"/>
       <c r="D18" s="110"/>
@@ -5692,7 +5698,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="111" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B19" s="111"/>
       <c r="C19" s="111"/>
@@ -5713,7 +5719,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="111" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B21" s="109"/>
       <c r="C21" s="109"/>
@@ -5723,7 +5729,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B22" s="109"/>
       <c r="C22" s="109"/>
@@ -5741,10 +5747,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
+        <v>597</v>
+      </c>
+      <c r="B23" s="109" t="s">
         <v>598</v>
-      </c>
-      <c r="B23" s="109" t="s">
-        <v>599</v>
       </c>
       <c r="C23" s="109"/>
       <c r="D23" s="110"/>
@@ -5756,10 +5762,10 @@
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
+        <v>599</v>
+      </c>
+      <c r="B24" s="109" t="s">
         <v>600</v>
-      </c>
-      <c r="B24" s="109" t="s">
-        <v>601</v>
       </c>
       <c r="C24" s="109"/>
       <c r="D24" s="110"/>
@@ -5771,10 +5777,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
+        <v>601</v>
+      </c>
+      <c r="B25" s="109" t="s">
         <v>602</v>
-      </c>
-      <c r="B25" s="109" t="s">
-        <v>603</v>
       </c>
       <c r="C25" s="109"/>
       <c r="D25" s="110"/>
@@ -6313,34 +6319,34 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="B55" s="5">
         <v>29613000</v>
       </c>
       <c r="C55" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B56" s="5">
         <v>7355000</v>
       </c>
       <c r="C56" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B57" s="5">
         <v>482000</v>
@@ -9338,7 +9344,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
+++ b/TAZA/_документы/Бюджет ТАЗА – 4 месяца (ноябрь–февраль).xlsx
@@ -388,7 +388,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="619">
   <si>
     <t>Статья</t>
   </si>
@@ -1776,9 +1776,6 @@
     <t>Заместитель руководителя ПО для ЦА</t>
   </si>
   <si>
-    <t>Менеджер проектов – эколог</t>
-  </si>
-  <si>
     <t>[Арманов Р.] Ведение проектов и закреплённых регионов, мониторинг мероприятий</t>
   </si>
   <si>
@@ -2151,9 +2148,6 @@
     <t>Мукашев Дархан</t>
   </si>
   <si>
-    <t>Менеджер проектов – эколог (отходы, вода, воздух)</t>
-  </si>
-  <si>
     <t>Проектный офис для Центральной Азии</t>
   </si>
   <si>
@@ -2272,6 +2266,9 @@
   </si>
   <si>
     <t>Октябрь-ноябрь 2026</t>
+  </si>
+  <si>
+    <t>Менеджер проектов</t>
   </si>
 </sst>
 </file>
@@ -3017,7 +3014,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -3025,19 +3022,19 @@
         <v>0</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C3" s="35" t="s">
+        <v>555</v>
+      </c>
+      <c r="D3" s="35" t="s">
         <v>556</v>
       </c>
-      <c r="D3" s="35" t="s">
-        <v>557</v>
-      </c>
       <c r="E3" s="35" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F3" s="35" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -3077,7 +3074,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="36" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B6" s="38">
         <f>(SUMPRODUCT((Штат!$E$5:$E$36="штат")*Штат!$K$5:$K$36*(Штат!$I$5:$I$36&lt;=2)))+B7+Обязательства_ЗП</f>
@@ -3102,7 +3099,7 @@
     </row>
     <row r="7" spans="1:6" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B7" s="38">
         <v>0</v>
@@ -3222,7 +3219,7 @@
     </row>
     <row r="12" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B12" s="38">
         <f>SUMIFS('Оснащение и офис'!$J$5:$J$77,'Оснащение и офис'!$A$5:$A$77,"Офис")+Обязательства_прочие</f>
@@ -3322,7 +3319,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B16" s="38">
         <f>(B15-Обязательства_ЗП-Обязательства_прочие-'Оснащение и офис'!$J$76)*Резерв</f>
@@ -3347,7 +3344,7 @@
     </row>
     <row r="17" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B17" s="38">
         <f>((B11+B12+B13+B14)-Обязательства_прочие-'Оснащение и офис'!$J$59-'Оснащение и офис'!$J$76)*(1+Резерв)*НДС+Обязательства_НДС+B19*НДС</f>
@@ -3422,7 +3419,7 @@
     </row>
     <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B20" s="40">
         <f>Обязательства_ЗП+Обязательства_НДС+Обязательства_прочие</f>
@@ -3444,7 +3441,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="43" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B21" s="44">
         <f>B18+B19</f>
@@ -3469,7 +3466,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="106" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B23" s="44">
         <f>B21</f>
@@ -3491,7 +3488,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="106" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B24" s="44"/>
       <c r="C24" s="44"/>
@@ -3503,7 +3500,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="43" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B25" s="44">
         <f>$F$24-B23</f>
@@ -4948,7 +4945,7 @@
         <v>186</v>
       </c>
       <c r="B20" s="104" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C20" s="104" t="s">
         <v>103</v>
@@ -4965,7 +4962,7 @@
         <v>4548</v>
       </c>
       <c r="G20" s="104" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5389,7 +5386,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="107" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -5397,30 +5394,30 @@
         <v>67</v>
       </c>
       <c r="B3" s="108" t="s">
+        <v>563</v>
+      </c>
+      <c r="C3" s="108" t="s">
         <v>564</v>
       </c>
-      <c r="C3" s="108" t="s">
+      <c r="D3" s="108" t="s">
         <v>565</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="E3" s="108" t="s">
         <v>566</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="F3" s="108" t="s">
         <v>567</v>
-      </c>
-      <c r="F3" s="108" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="109" t="s">
+        <v>568</v>
+      </c>
+      <c r="B4" s="109" t="s">
         <v>569</v>
       </c>
-      <c r="B4" s="109" t="s">
+      <c r="C4" s="109" t="s">
         <v>570</v>
-      </c>
-      <c r="C4" s="109" t="s">
-        <v>571</v>
       </c>
       <c r="D4" s="110">
         <v>1300000</v>
@@ -5439,10 +5436,10 @@
         <v>239</v>
       </c>
       <c r="B5" s="109" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C5" s="109" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D5" s="110">
         <v>1000000</v>
@@ -5461,10 +5458,10 @@
         <v>241</v>
       </c>
       <c r="B6" s="109" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C6" s="109" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D6" s="110">
         <v>700000</v>
@@ -5483,10 +5480,10 @@
         <v>241</v>
       </c>
       <c r="B7" s="109" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C7" s="109" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D7" s="110">
         <v>700000</v>
@@ -5505,10 +5502,10 @@
         <v>241</v>
       </c>
       <c r="B8" s="109" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C8" s="109" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D8" s="110">
         <v>700000</v>
@@ -5524,13 +5521,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="109" t="s">
+        <v>575</v>
+      </c>
+      <c r="B9" s="109" t="s">
         <v>576</v>
       </c>
-      <c r="B9" s="109" t="s">
+      <c r="C9" s="109" t="s">
         <v>577</v>
-      </c>
-      <c r="C9" s="109" t="s">
-        <v>578</v>
       </c>
       <c r="D9" s="110">
         <v>700000</v>
@@ -5544,15 +5541,15 @@
         <v>812210</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="109" t="s">
+        <v>618</v>
+      </c>
+      <c r="B10" s="109" t="s">
+        <v>578</v>
+      </c>
+      <c r="C10" s="109" t="s">
         <v>579</v>
-      </c>
-      <c r="B10" s="109" t="s">
-        <v>580</v>
-      </c>
-      <c r="C10" s="109" t="s">
-        <v>581</v>
       </c>
       <c r="D10" s="110">
         <v>800000</v>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="111" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B11" s="111"/>
       <c r="C11" s="111"/>
@@ -5595,7 +5592,7 @@
     </row>
     <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="111" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B13" s="109"/>
       <c r="C13" s="109"/>
@@ -5608,25 +5605,25 @@
         <v>173</v>
       </c>
       <c r="B14" s="108" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C14" s="108"/>
       <c r="D14" s="113" t="s">
         <v>71</v>
       </c>
       <c r="E14" s="113" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F14" s="113" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="109" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B15" s="109" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C15" s="109"/>
       <c r="D15" s="110">
@@ -5643,10 +5640,10 @@
     </row>
     <row r="16" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="109" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B16" s="109" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C16" s="109"/>
       <c r="D16" s="110">
@@ -5663,10 +5660,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="109" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B17" s="109" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C17" s="109"/>
       <c r="D17" s="110">
@@ -5686,7 +5683,7 @@
         <v>212</v>
       </c>
       <c r="B18" s="109" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C18" s="109"/>
       <c r="D18" s="110"/>
@@ -5698,7 +5695,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="111" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B19" s="111"/>
       <c r="C19" s="111"/>
@@ -5719,7 +5716,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="111" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B21" s="109"/>
       <c r="C21" s="109"/>
@@ -5729,7 +5726,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="109" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B22" s="109"/>
       <c r="C22" s="109"/>
@@ -5747,10 +5744,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="109" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B23" s="109" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C23" s="109"/>
       <c r="D23" s="110"/>
@@ -5762,10 +5759,10 @@
     </row>
     <row r="24" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="109" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B24" s="109" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C24" s="109"/>
       <c r="D24" s="110"/>
@@ -5777,10 +5774,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="109" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B25" s="109" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C25" s="109"/>
       <c r="D25" s="110"/>
@@ -6240,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -6319,40 +6316,40 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B55" s="5">
         <v>29613000</v>
       </c>
       <c r="C55" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B56" s="5">
         <v>7355000</v>
       </c>
       <c r="C56" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B57" s="5">
         <v>482000</v>
       </c>
       <c r="C57" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -6437,7 +6434,7 @@
         <v>314</v>
       </c>
       <c r="Q4" s="88" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="90" x14ac:dyDescent="0.25">
@@ -6681,7 +6678,7 @@
         <v>235</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>79</v>
@@ -7187,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="17" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q17" s="89"/>
     </row>
@@ -7244,7 +7241,7 @@
         <v>0</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="Q18" s="89"/>
     </row>
@@ -7316,7 +7313,7 @@
         <v>235</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>79</v>
@@ -7432,7 +7429,7 @@
         <v>245</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>79</v>
@@ -8060,7 +8057,7 @@
         <v>354</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>454</v>
+        <v>618</v>
       </c>
       <c r="D33" s="17" t="s">
         <v>449</v>
@@ -8117,7 +8114,7 @@
         <v>354</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>454</v>
+        <v>618</v>
       </c>
       <c r="D34" s="17" t="s">
         <v>449</v>
@@ -8346,12 +8343,12 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C41" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C42" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H42" s="5">
         <f>SUMPRODUCT(Q5:Q36,H5:H36)</f>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H43" s="5">
         <f>H42*(Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС))</f>
@@ -8369,7 +8366,7 @@
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C44" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H44" s="6">
         <f>H42+H43</f>
@@ -8378,7 +8375,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -8429,10 +8426,10 @@
         <v>273</v>
       </c>
       <c r="F3" s="103" t="s">
+        <v>511</v>
+      </c>
+      <c r="G3" s="103" t="s">
         <v>512</v>
-      </c>
-      <c r="G3" s="103" t="s">
-        <v>513</v>
       </c>
       <c r="H3" s="25" t="s">
         <v>274</v>
@@ -8455,7 +8452,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>204</v>
@@ -8794,7 +8791,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
@@ -8816,12 +8813,12 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8832,48 +8829,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B4" s="93">
         <v>0.1</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B5" s="94">
         <f>Ставка_ОПВР+Ставка_ООСМС+Ставка_СН*(1-Ставка_ОПВ-Ставка_ВОСМС)</f>
         <v>0.1178</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="95" t="s">
+        <v>493</v>
+      </c>
+      <c r="B7" s="95" t="s">
         <v>494</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="C7" s="95" t="s">
         <v>495</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="D7" s="95" t="s">
         <v>496</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="E7" s="95" t="s">
         <v>497</v>
       </c>
-      <c r="E7" s="95" t="s">
+      <c r="F7" s="95" t="s">
         <v>498</v>
       </c>
-      <c r="F7" s="95" t="s">
+      <c r="G7" s="95" t="s">
         <v>499</v>
-      </c>
-      <c r="G7" s="95" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8994,48 +8991,48 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="98" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B14" s="97">
         <f>$B$4*(1+$B$5)</f>
         <v>0.11177999999999999</v>
       </c>
       <c r="C14" s="98" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="98" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B15" s="97">
         <f>$B$4*(1+$B$5)*(1+НДС)</f>
         <v>0.12966479999999997</v>
       </c>
       <c r="C15" s="98" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="99" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B18" s="99"/>
       <c r="C18" s="99"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="98" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B19" s="96">
         <f>Аутсорс!E11</f>
@@ -9045,7 +9042,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="98" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B20" s="96">
         <f>Аутсорс!F11</f>
@@ -9055,7 +9052,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="100" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B21" s="101">
         <f>Аутсорс!F11*2</f>
@@ -9065,7 +9062,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="100" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B22" s="101">
         <f>B21*(1+НДС)</f>
@@ -9075,7 +9072,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="98" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B23" s="96">
         <f>Аутсорс!L11</f>
@@ -9085,7 +9082,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>
@@ -9237,7 +9234,7 @@
     </row>
     <row r="9" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C9">
         <f>SUMIFS(Штат!$G$5:$G$36,Штат!$B$5:$B$36,"Департамент проектного управления*",Штат!$E$5:$E$36,"штат")</f>
@@ -9344,7 +9341,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9381,16 +9378,16 @@
         <v>90</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9506,7 +9503,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
@@ -9533,7 +9530,7 @@
         <v>97</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
@@ -9552,7 +9549,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
@@ -9579,7 +9576,7 @@
         <v>97</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C9" s="80" t="s">
         <v>99</v>
@@ -9598,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" ref="I9" si="4">IF(F9="разово",IF(G9&lt;=3,D9*E9,0),IF(F9="мес",D9*E9*MAX(0,4-G9),D9*E9*MAX(0,4-G9)/12))</f>
@@ -9625,7 +9622,7 @@
         <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C10" s="81" t="s">
         <v>99</v>
@@ -9644,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10" si="5">IF(F10="разово",IF(G10&lt;=3,D10*E10,0),IF(F10="мес",D10*E10*MAX(0,4-G10),D10*E10*MAX(0,4-G10)/12))</f>
@@ -9671,7 +9668,7 @@
         <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C11" s="82" t="s">
         <v>99</v>
@@ -9690,7 +9687,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11" si="6">IF(F11="разово",IF(G11&lt;=3,D11*E11,0),IF(F11="мес",D11*E11*MAX(0,4-G11),D11*E11*MAX(0,4-G11)/12))</f>
@@ -9717,7 +9714,7 @@
         <v>97</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C12" t="s">
         <v>99</v>
@@ -9736,7 +9733,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
@@ -9763,7 +9760,7 @@
         <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C13" s="84" t="s">
         <v>99</v>
@@ -9782,7 +9779,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="I13" s="5">
         <f>IF(F13="разово",IF(G13&lt;=3,D13*E13,0),IF(F13="мес",D13*E13*MAX(0,4-G13),D13*E13*MAX(0,4-G13)/12))</f>
@@ -9809,7 +9806,7 @@
         <v>97</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C14" s="84" t="s">
         <v>99</v>
@@ -9828,7 +9825,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I14" s="5">
         <f>IF(F14="разово",IF(G14&lt;=3,D14*E14,0),IF(F14="мес",D14*E14*MAX(0,4-G14),D14*E14*MAX(0,4-G14)/12))</f>
@@ -9855,7 +9852,7 @@
         <v>97</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C15" s="83" t="s">
         <v>99</v>
@@ -9874,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" ref="I15" si="7">IF(F15="разово",IF(G15&lt;=3,D15*E15,0),IF(F15="мес",D15*E15*MAX(0,4-G15),D15*E15*MAX(0,4-G15)/12))</f>
@@ -9901,7 +9898,7 @@
         <v>97</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C16" s="92" t="s">
         <v>99</v>
@@ -9920,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" ref="I16:I21" si="8">IF(F16="разово",IF(G16&lt;=3,D16*E16,0),IF(F16="мес",D16*E16*MAX(0,4-G16),D16*E16*MAX(0,4-G16)/12))</f>
@@ -9947,7 +9944,7 @@
         <v>97</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C17" s="87" t="s">
         <v>103</v>
@@ -9966,7 +9963,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="8"/>
@@ -9993,7 +9990,7 @@
         <v>97</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C18" s="91" t="s">
         <v>103</v>
@@ -10012,7 +10009,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="8"/>
@@ -10039,7 +10036,7 @@
         <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C19" s="85" t="s">
         <v>99</v>
@@ -10058,7 +10055,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I19" s="5">
         <f t="shared" si="8"/>
@@ -10085,7 +10082,7 @@
         <v>97</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C20" s="86" t="s">
         <v>103</v>
@@ -10104,7 +10101,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="I20" s="5">
         <f t="shared" si="8"/>
@@ -10131,7 +10128,7 @@
         <v>97</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C21" s="86" t="s">
         <v>103</v>
@@ -10150,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="8"/>
@@ -10263,7 +10260,7 @@
         <v>97</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -10281,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="0"/>
@@ -10399,7 +10396,7 @@
         <v>97</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C27" s="86" t="s">
         <v>103</v>
@@ -10418,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I27" s="5">
         <f>IF(F27="разово",IF(G27&lt;=3,D27*E27,0),IF(F27="мес",D27*E27*MAX(0,4-G27),D27*E27*MAX(0,4-G27)/12))</f>
@@ -11074,7 +11071,7 @@
         <v>97</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C42" s="105" t="s">
         <v>99</v>
@@ -11093,7 +11090,7 @@
         <v>1</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I42" s="5">
         <f>IF(F42="разово",IF(G42&lt;=3,D42*E42,0),IF(F42="мес",D42*E42*MAX(0,4-G42),D42*E42*MAX(0,4-G42)/12))</f>
@@ -11166,7 +11163,7 @@
         <v>97</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C44" t="s">
         <v>99</v>
@@ -11185,7 +11182,7 @@
         <v>1</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="0"/>
@@ -11212,7 +11209,7 @@
         <v>97</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C45" s="90" t="s">
         <v>99</v>
@@ -11231,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I45" s="5">
         <f>IF(F45="разово",IF(G45&lt;=3,D45*E45,0),IF(F45="мес",D45*E45*MAX(0,4-G45),D45*E45*MAX(0,4-G45)/12))</f>
@@ -11258,7 +11255,7 @@
         <v>97</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -11276,7 +11273,7 @@
         <v>1</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="0"/>
@@ -11526,7 +11523,7 @@
         <v>97</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C52" t="s">
         <v>99</v>
@@ -11545,7 +11542,7 @@
         <v>1</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="I52" s="5">
         <f t="shared" ref="I52:I54" si="14">IF(F52="разово",IF(G52&lt;=3,D52*E52,0),IF(F52="мес",D52*E52*MAX(0,4-G52),D52*E52*MAX(0,4-G52)/12))</f>
@@ -11572,7 +11569,7 @@
         <v>97</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -11591,7 +11588,7 @@
         <v>1</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="14"/>
@@ -11901,7 +11898,7 @@
         <v>2</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="15"/>
@@ -12008,10 +12005,10 @@
         <v>111</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="C63" s="105" t="s">
         <v>552</v>
-      </c>
-      <c r="C63" s="105" t="s">
-        <v>553</v>
       </c>
       <c r="D63" s="9">
         <v>2</v>
@@ -12027,7 +12024,7 @@
         <v>2</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I63" s="5">
         <f>IF(F63="разово",IF(G63&lt;=3,D63*E63,0),IF(F63="мес",D63*E63*MAX(0,4-G63),D63*E63*MAX(0,4-G63)/12))</f>
@@ -12351,7 +12348,7 @@
         <v>121</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C71" t="s">
         <v>126</v>
@@ -12370,7 +12367,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="15"/>
@@ -12397,10 +12394,10 @@
         <v>121</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C72" s="102" t="s">
         <v>509</v>
-      </c>
-      <c r="C72" s="102" t="s">
-        <v>510</v>
       </c>
       <c r="D72" s="9">
         <v>1</v>
@@ -12415,7 +12412,7 @@
         <v>2</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I72" s="5">
         <f>IF(F72="разово",IF(G72&lt;=3,D72*E72,0),IF(F72="мес",D72*E72*MAX(0,4-G72),D72*E72*MAX(0,4-G72)/12))</f>
@@ -12556,7 +12553,7 @@
         <v>111</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C76" t="s">
         <v>103</v>
@@ -12574,7 +12571,7 @@
         <v>1</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I76" s="5">
         <f t="shared" si="15"/>
@@ -12664,13 +12661,13 @@
         <v>90</v>
       </c>
       <c r="H4" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>555</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>556</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="30" x14ac:dyDescent="0.25">
